--- a/PYPL.xlsx
+++ b/PYPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6741CAEC-3251-4055-ABB0-F347E54C5E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DCD3D0-DF80-499F-90C7-FB6B2207FE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{B690896D-DF4D-4BA1-A25A-CD8C19559281}"/>
+    <workbookView xWindow="225" yWindow="3900" windowWidth="38175" windowHeight="15240" xr2:uid="{B690896D-DF4D-4BA1-A25A-CD8C19559281}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="342">
   <si>
     <t>PYPL</t>
   </si>
@@ -1085,6 +1085,9 @@
   </si>
   <si>
     <t>Alex Chriss (CEO 2023 - 2025)</t>
+  </si>
+  <si>
+    <t>Paypal potential candidate for Takeover (https://finance.yahoo.com/news/paypal-faces-takeover-talk-ai-221058219.html?guccounter=1&amp;guce_referrer=aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS8&amp;guce_referrer_sig=AQAAADvebTLk8diE1pdvprcTUyH1RRbW6aRvjvFzRUYfnIHXBL10fNG_DM_aensxTpeyxmAAKZUak8aw5PPdMSyGeC0dHMxttNiuqbya5St_2_xzQtHpAIH16cXnDjrJkyVOak4uLBUTq69Zy3mgw1wX8oVw4F7_zIewFOntMvGyy4vD)</t>
   </si>
 </sst>
 </file>
@@ -1100,13 +1103,19 @@
     <numFmt numFmtId="169" formatCode="0.0"/>
     <numFmt numFmtId="170" formatCode="\F\Y#,##0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1420,146 +1429,147 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="15" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="16" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2071,7 +2081,7 @@
       <c r="I3" s="3">
         <v>931</v>
       </c>
-      <c r="J3" s="82" t="s">
+      <c r="J3" s="76" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2098,7 +2108,7 @@
         <f>8049+2373</f>
         <v>10422</v>
       </c>
-      <c r="J5" s="82" t="s">
+      <c r="J5" s="76" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2109,7 +2119,7 @@
       <c r="I6" s="3">
         <v>9987</v>
       </c>
-      <c r="J6" s="82" t="s">
+      <c r="J6" s="76" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2172,7 +2182,7 @@
       <c r="J13" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="K13" s="81" t="s">
+      <c r="K13" s="75" t="s">
         <v>338</v>
       </c>
     </row>
@@ -2197,7 +2207,7 @@
       <c r="K15" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="M15" s="81" t="s">
+      <c r="M15" s="75" t="s">
         <v>335</v>
       </c>
     </row>
@@ -2221,10 +2231,10 @@
       <c r="B18" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="J18" s="81" t="s">
+      <c r="J18" s="75" t="s">
         <v>339</v>
       </c>
-      <c r="K18" s="81" t="s">
+      <c r="K18" s="75" t="s">
         <v>340</v>
       </c>
     </row>
@@ -2255,6 +2265,9 @@
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B23" s="84" t="s">
+        <v>341</v>
+      </c>
       <c r="I23" s="3"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
@@ -2354,7 +2367,7 @@
       <c r="X2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="Y2" s="82" t="s">
+      <c r="Y2" s="76" t="s">
         <v>336</v>
       </c>
       <c r="Z2" s="4"/>
@@ -5540,27 +5553,27 @@
         <v>0.23081192007869733</v>
       </c>
       <c r="T39" s="11">
-        <f>+T12/S12-1</f>
+        <f t="shared" ref="T39:Y39" si="58">+T12/S12-1</f>
         <v>0.31483232082031121</v>
       </c>
       <c r="U39" s="11">
-        <f>+U12/T12-1</f>
+        <f t="shared" si="58"/>
         <v>0.33097914454384436</v>
       </c>
       <c r="V39" s="11">
-        <f>+V12/U12-1</f>
+        <f t="shared" si="58"/>
         <v>8.9280740746091825E-2</v>
       </c>
       <c r="W39" s="11">
-        <f>+W12/V12-1</f>
+        <f t="shared" si="58"/>
         <v>0.12634697799444705</v>
       </c>
       <c r="X39" s="11">
-        <f>+X12/W12-1</f>
+        <f t="shared" si="58"/>
         <v>9.9812309340897576E-2</v>
       </c>
       <c r="Y39" s="11">
-        <f>+Y12/X12-1</f>
+        <f t="shared" si="58"/>
         <v>6.711417779496176E-2</v>
       </c>
       <c r="Z39" s="11"/>
@@ -5592,70 +5605,70 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="11">
-        <f t="shared" ref="G40:M42" si="58">+G17/C17-1</f>
+        <f t="shared" ref="G40:M42" si="59">+G17/C17-1</f>
         <v>0.10527969830295403</v>
       </c>
       <c r="H40" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>1.6917827694057364E-2</v>
       </c>
       <c r="I40" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>6.2067929065223959E-2</v>
       </c>
       <c r="J40" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4.1878346835095392E-2</v>
       </c>
       <c r="K40" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>-2.5589991470003071E-3</v>
       </c>
       <c r="L40" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4.0262826785963934E-2</v>
       </c>
       <c r="M40" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>6.438375548323183E-2</v>
       </c>
       <c r="N40" s="11"/>
       <c r="O40" s="11"/>
       <c r="P40" s="11"/>
       <c r="Q40" s="11">
-        <f t="shared" ref="Q40:S40" si="59">+Q17/P17-1</f>
+        <f t="shared" ref="Q40:S40" si="60">+Q17/P17-1</f>
         <v>0.19989567031820554</v>
       </c>
       <c r="R40" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.19198330579949574</v>
       </c>
       <c r="S40" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.17433802611423155</v>
       </c>
       <c r="T40" s="11">
-        <f t="shared" ref="T40:Y42" si="60">+T17/S17-1</f>
+        <f t="shared" ref="T40:Y42" si="61">+T17/S17-1</f>
         <v>0.23721970308714835</v>
       </c>
       <c r="U40" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.17491716035746552</v>
       </c>
       <c r="V40" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>7.7087428424921001E-2</v>
       </c>
       <c r="W40" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>6.5500277711656008E-2</v>
       </c>
       <c r="X40" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>7.3909967606210714E-2</v>
       </c>
       <c r="Y40" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>3.314610637265103E-2</v>
       </c>
       <c r="Z40" s="11"/>
@@ -5687,70 +5700,70 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>-1.6272189349112454E-2</v>
       </c>
       <c r="H41" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.10075187969924815</v>
       </c>
       <c r="I41" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>2.0942408376963373E-2</v>
       </c>
       <c r="J41" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4.7106325706594898E-2</v>
       </c>
       <c r="K41" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.16541353383458657</v>
       </c>
       <c r="L41" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.15710382513661192</v>
       </c>
       <c r="M41" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.14743589743589736</v>
       </c>
       <c r="N41" s="11"/>
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
       <c r="Q41" s="11">
-        <f t="shared" ref="Q41:S41" si="61">+Q18/P18-1</f>
+        <f t="shared" ref="Q41:S41" si="62">+Q18/P18-1</f>
         <v>0.26730310262529833</v>
       </c>
       <c r="R41" s="11">
+        <f t="shared" si="62"/>
+        <v>9.3534212178280063E-2</v>
+      </c>
+      <c r="S41" s="11">
+        <f t="shared" si="62"/>
+        <v>-3.960964408725598E-2</v>
+      </c>
+      <c r="T41" s="11">
         <f t="shared" si="61"/>
-        <v>9.3534212178280063E-2</v>
-      </c>
-      <c r="S41" s="11">
+        <v>-8.1888822474596501E-2</v>
+      </c>
+      <c r="U41" s="11">
         <f t="shared" si="61"/>
-        <v>-3.960964408725598E-2</v>
-      </c>
-      <c r="T41" s="11">
-        <f t="shared" si="60"/>
-        <v>-8.1888822474596501E-2</v>
-      </c>
-      <c r="U41" s="11">
-        <f t="shared" si="60"/>
         <v>0.28190104166666674</v>
       </c>
       <c r="V41" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.17420010157440324</v>
       </c>
       <c r="W41" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.26038062283737018</v>
       </c>
       <c r="X41" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>1.4070006863418083E-2</v>
       </c>
       <c r="Y41" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.14179357021996619</v>
       </c>
       <c r="Z41" s="11"/>
@@ -5782,70 +5795,70 @@
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>9.3607954545454453E-2</v>
       </c>
       <c r="H42" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>8.2063949499108002E-2</v>
       </c>
       <c r="I42" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>5.7832299811269916E-2</v>
       </c>
       <c r="J42" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4.2362322452030865E-2</v>
       </c>
       <c r="K42" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>1.1949603844655154E-2</v>
       </c>
       <c r="L42" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>5.1109701965757814E-2</v>
       </c>
       <c r="M42" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>7.2639225181598155E-2</v>
       </c>
       <c r="N42" s="13"/>
       <c r="O42" s="11"/>
       <c r="P42" s="13"/>
       <c r="Q42" s="13">
-        <f t="shared" ref="Q42:S42" si="62">+Q19/P19-1</f>
+        <f t="shared" ref="Q42:S42" si="63">+Q19/P19-1</f>
         <v>0.20771075447334431</v>
       </c>
       <c r="R42" s="13">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.18000610966855057</v>
       </c>
       <c r="S42" s="13">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.15021681444566704</v>
       </c>
       <c r="T42" s="13">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.20717983344586988</v>
       </c>
       <c r="U42" s="13">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.18257667567819524</v>
       </c>
       <c r="V42" s="13">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>8.4624177210200546E-2</v>
       </c>
       <c r="W42" s="13">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>8.1873682680427384E-2</v>
       </c>
       <c r="X42" s="13">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>6.8052803063383793E-2</v>
       </c>
       <c r="Y42" s="13">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>4.3243073245903707E-2</v>
       </c>
       <c r="Z42" s="13"/>
@@ -5873,89 +5886,89 @@
         <v>42</v>
       </c>
       <c r="C43" s="11">
-        <f t="shared" ref="C43:J43" si="63">+C22/C19</f>
+        <f t="shared" ref="C43:J43" si="64">+C22/C19</f>
         <v>0.47088068181818182</v>
       </c>
       <c r="D43" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.45944833264717994</v>
       </c>
       <c r="E43" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.45416554327311942</v>
       </c>
       <c r="F43" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.45751308248193373</v>
       </c>
       <c r="G43" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.44953890115599426</v>
       </c>
       <c r="H43" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.45757767913760306</v>
       </c>
       <c r="I43" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.46565566458519181</v>
       </c>
       <c r="J43" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.47035620368156827</v>
       </c>
       <c r="K43" s="11">
-        <f t="shared" ref="K43:L43" si="64">+K22/K19</f>
+        <f t="shared" ref="K43:L43" si="65">+K22/K19</f>
         <v>0.4769605955589783</v>
       </c>
       <c r="L43" s="11">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.46380308880308879</v>
       </c>
       <c r="M43" s="11">
-        <f t="shared" ref="M43" si="65">+M22/M19</f>
+        <f t="shared" ref="M43" si="66">+M22/M19</f>
         <v>0.45990257811571816</v>
       </c>
       <c r="N43" s="11"/>
       <c r="O43" s="11"/>
       <c r="P43" s="11">
-        <f t="shared" ref="P43:S43" si="66">+P22/P19</f>
+        <f t="shared" ref="P43:S43" si="67">+P22/P19</f>
         <v>0.5242575170632725</v>
       </c>
       <c r="Q43" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.52382770734687645</v>
       </c>
       <c r="R43" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.50611610898970938</v>
       </c>
       <c r="S43" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.54028809363042984</v>
       </c>
       <c r="T43" s="11">
-        <f>+T22/T19</f>
+        <f t="shared" ref="T43:Y43" si="68">+T22/T19</f>
         <v>0.54903514496131256</v>
       </c>
       <c r="U43" s="11">
-        <f>+U22/U19</f>
+        <f t="shared" si="68"/>
         <v>0.55165346261479642</v>
       </c>
       <c r="V43" s="11">
-        <f>+V22/V19</f>
+        <f t="shared" si="68"/>
         <v>0.50050875790391747</v>
       </c>
       <c r="W43" s="11">
-        <f>+W22/W19</f>
+        <f t="shared" si="68"/>
         <v>0.46031372812468507</v>
       </c>
       <c r="X43" s="11">
-        <f>+X22/X19</f>
+        <f t="shared" si="68"/>
         <v>0.46098688555524103</v>
       </c>
       <c r="Y43" s="11">
-        <f>+Y22/Y19</f>
+        <f t="shared" si="68"/>
         <v>0.46620643916556131</v>
       </c>
       <c r="Z43" s="11"/>
@@ -5983,89 +5996,89 @@
         <v>43</v>
       </c>
       <c r="C44" s="11">
-        <f t="shared" ref="C44:J44" si="67">+C28/C19</f>
+        <f t="shared" ref="C44:J44" si="69">+C28/C19</f>
         <v>0.14190340909090909</v>
       </c>
       <c r="D44" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>0.15548236585700562</v>
       </c>
       <c r="E44" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>0.15745483957940146</v>
       </c>
       <c r="F44" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>0.21530027410914529</v>
       </c>
       <c r="G44" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>0.15170801402779582</v>
       </c>
       <c r="H44" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>0.16804058338617628</v>
       </c>
       <c r="I44" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>0.17726519689053141</v>
       </c>
       <c r="J44" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>0.17224480038250059</v>
       </c>
       <c r="K44" s="11">
-        <f t="shared" ref="K44:L44" si="68">+K28/K19</f>
+        <f t="shared" ref="K44:L44" si="70">+K28/K19</f>
         <v>0.19638043896804006</v>
       </c>
       <c r="L44" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>0.18146718146718147</v>
       </c>
       <c r="M44" s="11">
-        <f t="shared" ref="M44" si="69">+M28/M19</f>
+        <f t="shared" ref="M44" si="71">+M28/M19</f>
         <v>0.18058690744920994</v>
       </c>
       <c r="N44" s="11"/>
       <c r="O44" s="11"/>
       <c r="P44" s="11">
-        <f t="shared" ref="P44:R44" si="70">+P28/P19</f>
+        <f t="shared" ref="P44:R44" si="72">+P28/P19</f>
         <v>0.14628297362110312</v>
       </c>
       <c r="Q44" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.16244081258591722</v>
       </c>
       <c r="R44" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.1419972817293379</v>
       </c>
       <c r="S44" s="11">
-        <f t="shared" ref="S44:X44" si="71">+S28/S19</f>
+        <f t="shared" ref="S44:X44" si="73">+S28/S19</f>
         <v>0.15299347287868556</v>
       </c>
       <c r="T44" s="11">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.15330474503589075</v>
       </c>
       <c r="U44" s="11">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.16798707185369122</v>
       </c>
       <c r="V44" s="11">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.13943600552365723</v>
       </c>
       <c r="W44" s="11">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.16888918746431092</v>
       </c>
       <c r="X44" s="11">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.16746862911595434</v>
       </c>
       <c r="Y44" s="11">
-        <f t="shared" ref="Y44" si="72">+Y28/Y19</f>
+        <f t="shared" ref="Y44" si="74">+Y28/Y19</f>
         <v>0.1828349210177258</v>
       </c>
       <c r="Z44" s="11"/>
@@ -6093,27 +6106,27 @@
         <v>44</v>
       </c>
       <c r="C45" s="11">
-        <f t="shared" ref="C45:H45" si="73">+C31/C30</f>
+        <f t="shared" ref="C45:H45" si="75">+C31/C30</f>
         <v>0.25977653631284914</v>
       </c>
       <c r="D45" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.21028396009209516</v>
       </c>
       <c r="E45" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.17808219178082191</v>
       </c>
       <c r="F45" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.2180702732849972</v>
       </c>
       <c r="G45" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.26550868486352358</v>
       </c>
       <c r="H45" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.1937097927090779</v>
       </c>
       <c r="I45" s="11">
@@ -6121,15 +6134,15 @@
         <v>0.2295957284515637</v>
       </c>
       <c r="J45" s="11">
-        <f t="shared" ref="J45:X45" si="74">+J31/J30</f>
+        <f t="shared" ref="J45:X45" si="76">+J31/J30</f>
         <v>0.20496453900709219</v>
       </c>
       <c r="K45" s="11">
-        <f t="shared" ref="K45:L45" si="75">+K31/K30</f>
+        <f t="shared" ref="K45:L45" si="77">+K31/K30</f>
         <v>0.19713038053649407</v>
       </c>
       <c r="L45" s="11">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>0.17593198168737736</v>
       </c>
       <c r="M45" s="11">
@@ -6139,43 +6152,43 @@
       <c r="N45" s="11"/>
       <c r="O45" s="11"/>
       <c r="P45" s="11">
-        <f t="shared" ref="P45:R45" si="76">+P31/P30</f>
+        <f t="shared" ref="P45:R45" si="78">+P31/P30</f>
         <v>0.14101778050275904</v>
       </c>
       <c r="Q45" s="11">
+        <f t="shared" si="78"/>
+        <v>0.18409090909090908</v>
+      </c>
+      <c r="R45" s="11">
+        <f t="shared" si="78"/>
+        <v>0.13425925925925927</v>
+      </c>
+      <c r="S45" s="11">
         <f t="shared" si="76"/>
-        <v>0.18409090909090908</v>
-      </c>
-      <c r="R45" s="11">
+        <v>0.17978652434956638</v>
+      </c>
+      <c r="T45" s="11">
+        <f t="shared" ref="T45:U45" si="79">+T31/T30</f>
+        <v>0.17038499506416585</v>
+      </c>
+      <c r="U45" s="11">
+        <f t="shared" si="79"/>
+        <v>-1.7077335935594046E-2</v>
+      </c>
+      <c r="V45" s="11">
         <f t="shared" si="76"/>
-        <v>0.13425925925925927</v>
-      </c>
-      <c r="S45" s="11">
-        <f t="shared" si="74"/>
-        <v>0.17978652434956638</v>
-      </c>
-      <c r="T45" s="11">
-        <f t="shared" ref="T45:U45" si="77">+T31/T30</f>
-        <v>0.17038499506416585</v>
-      </c>
-      <c r="U45" s="11">
-        <f t="shared" si="77"/>
-        <v>-1.7077335935594046E-2</v>
-      </c>
-      <c r="V45" s="11">
-        <f t="shared" si="74"/>
         <v>0.28134284016636957</v>
       </c>
       <c r="W45" s="11">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>0.21530216226205878</v>
       </c>
       <c r="X45" s="11">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>0.22180521673860012</v>
       </c>
       <c r="Y45" s="11">
-        <f t="shared" ref="Y45" si="78">+Y31/Y30</f>
+        <f t="shared" ref="Y45" si="80">+Y31/Y30</f>
         <v>0.16830896376350921</v>
       </c>
       <c r="Z45" s="11"/>
@@ -6489,7 +6502,7 @@
       </c>
     </row>
     <row r="53" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B53" s="81" t="s">
+      <c r="B53" s="75" t="s">
         <v>337</v>
       </c>
       <c r="C53" s="3"/>
@@ -6552,31 +6565,31 @@
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="Q54" s="17">
-        <f t="shared" ref="Q54:W54" si="79">+SUM(Q48:Q53)</f>
+        <f t="shared" ref="Q54:W54" si="81">+SUM(Q48:Q53)</f>
         <v>32645</v>
       </c>
       <c r="R54" s="17">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>32963</v>
       </c>
       <c r="S54" s="17">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>38495</v>
       </c>
       <c r="T54" s="17">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>50995</v>
       </c>
       <c r="U54" s="17">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>52574</v>
       </c>
       <c r="V54" s="17">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>57517</v>
       </c>
       <c r="W54" s="17">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>62569</v>
       </c>
       <c r="X54" s="17">
@@ -6839,23 +6852,23 @@
         <v>10369</v>
       </c>
       <c r="S60" s="17">
-        <f t="shared" ref="S60:W60" si="80">+SUM(S55:S59)</f>
+        <f t="shared" ref="S60:W60" si="82">+SUM(S55:S59)</f>
         <v>12838</v>
       </c>
       <c r="T60" s="17">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>19384</v>
       </c>
       <c r="U60" s="17">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>23229</v>
       </c>
       <c r="V60" s="17">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>21200</v>
       </c>
       <c r="W60" s="17">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>19597</v>
       </c>
       <c r="X60" s="17">
@@ -6884,40 +6897,40 @@
       <c r="M61" s="9"/>
       <c r="N61" s="9"/>
       <c r="O61" s="9"/>
-      <c r="P61" s="83"/>
-      <c r="Q61" s="83">
+      <c r="P61" s="77"/>
+      <c r="Q61" s="77">
         <f>+Q60+Q54</f>
         <v>40774</v>
       </c>
-      <c r="R61" s="83">
+      <c r="R61" s="77">
         <f>+R60+R54</f>
         <v>43332</v>
       </c>
-      <c r="S61" s="83">
-        <f t="shared" ref="S61:W61" si="81">+S60+S54</f>
+      <c r="S61" s="77">
+        <f t="shared" ref="S61:W61" si="83">+S60+S54</f>
         <v>51333</v>
       </c>
-      <c r="T61" s="83">
-        <f t="shared" si="81"/>
+      <c r="T61" s="77">
+        <f t="shared" si="83"/>
         <v>70379</v>
       </c>
-      <c r="U61" s="83">
-        <f t="shared" si="81"/>
+      <c r="U61" s="77">
+        <f t="shared" si="83"/>
         <v>75803</v>
       </c>
-      <c r="V61" s="83">
-        <f t="shared" si="81"/>
+      <c r="V61" s="77">
+        <f t="shared" si="83"/>
         <v>78717</v>
       </c>
-      <c r="W61" s="83">
-        <f t="shared" si="81"/>
+      <c r="W61" s="77">
+        <f t="shared" si="83"/>
         <v>82166</v>
       </c>
-      <c r="X61" s="83">
+      <c r="X61" s="77">
         <f>+X60+X54</f>
         <v>81611</v>
       </c>
-      <c r="Y61" s="83">
+      <c r="Y61" s="77">
         <f>+Y60+Y54</f>
         <v>80173</v>
       </c>
@@ -7130,35 +7143,35 @@
         <v>22863</v>
       </c>
       <c r="R66" s="17">
-        <f t="shared" ref="R66:Y66" si="82">+SUM(R62:R65)</f>
+        <f t="shared" ref="R66:Y66" si="84">+SUM(R62:R65)</f>
         <v>25904</v>
       </c>
       <c r="S66" s="17">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>26919</v>
       </c>
       <c r="T66" s="17">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>38447</v>
       </c>
       <c r="U66" s="17">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>43029</v>
       </c>
       <c r="V66" s="17">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>45101</v>
       </c>
       <c r="W66" s="17">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>48466</v>
       </c>
       <c r="X66" s="17">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>48376</v>
       </c>
       <c r="Y66" s="17">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>46443</v>
       </c>
     </row>
@@ -7270,27 +7283,27 @@
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
       <c r="Q69" s="17">
-        <f t="shared" ref="Q69:V69" si="83">+SUM(Q67:Q68)</f>
+        <f t="shared" ref="Q69:V69" si="85">+SUM(Q67:Q68)</f>
         <v>1917</v>
       </c>
       <c r="R69" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>2042</v>
       </c>
       <c r="S69" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>7485</v>
       </c>
       <c r="T69" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>11869</v>
       </c>
       <c r="U69" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>11047</v>
       </c>
       <c r="V69" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>13342</v>
       </c>
       <c r="W69" s="17">
@@ -7323,40 +7336,40 @@
       <c r="M70" s="9"/>
       <c r="N70" s="9"/>
       <c r="O70" s="9"/>
-      <c r="P70" s="83"/>
-      <c r="Q70" s="83">
-        <f t="shared" ref="Q70:W70" si="84">+Q69+Q66</f>
+      <c r="P70" s="77"/>
+      <c r="Q70" s="77">
+        <f t="shared" ref="Q70:W70" si="86">+Q69+Q66</f>
         <v>24780</v>
       </c>
-      <c r="R70" s="83">
-        <f t="shared" si="84"/>
+      <c r="R70" s="77">
+        <f t="shared" si="86"/>
         <v>27946</v>
       </c>
-      <c r="S70" s="83">
-        <f t="shared" si="84"/>
+      <c r="S70" s="77">
+        <f t="shared" si="86"/>
         <v>34404</v>
       </c>
-      <c r="T70" s="83">
-        <f t="shared" si="84"/>
+      <c r="T70" s="77">
+        <f t="shared" si="86"/>
         <v>50316</v>
       </c>
-      <c r="U70" s="83">
-        <f t="shared" si="84"/>
+      <c r="U70" s="77">
+        <f t="shared" si="86"/>
         <v>54076</v>
       </c>
-      <c r="V70" s="83">
-        <f t="shared" si="84"/>
+      <c r="V70" s="77">
+        <f t="shared" si="86"/>
         <v>58443</v>
       </c>
-      <c r="W70" s="83">
-        <f t="shared" si="84"/>
+      <c r="W70" s="77">
+        <f t="shared" si="86"/>
         <v>61115</v>
       </c>
-      <c r="X70" s="83">
+      <c r="X70" s="77">
         <f>+X69+X66</f>
         <v>61194</v>
       </c>
-      <c r="Y70" s="83">
+      <c r="Y70" s="77">
         <f>+Y69+Y66</f>
         <v>59917</v>
       </c>
@@ -7423,40 +7436,40 @@
       <c r="M72" s="9"/>
       <c r="N72" s="9"/>
       <c r="O72" s="9"/>
-      <c r="P72" s="83"/>
-      <c r="Q72" s="83">
-        <f t="shared" ref="Q72:W72" si="85">+Q70+Q71</f>
+      <c r="P72" s="77"/>
+      <c r="Q72" s="77">
+        <f t="shared" ref="Q72:W72" si="87">+Q70+Q71</f>
         <v>40774</v>
       </c>
-      <c r="R72" s="83">
-        <f t="shared" si="85"/>
+      <c r="R72" s="77">
+        <f t="shared" si="87"/>
         <v>43332</v>
       </c>
-      <c r="S72" s="83">
-        <f t="shared" si="85"/>
+      <c r="S72" s="77">
+        <f t="shared" si="87"/>
         <v>51333</v>
       </c>
-      <c r="T72" s="83">
-        <f t="shared" si="85"/>
+      <c r="T72" s="77">
+        <f t="shared" si="87"/>
         <v>70379</v>
       </c>
-      <c r="U72" s="83">
-        <f t="shared" si="85"/>
+      <c r="U72" s="77">
+        <f t="shared" si="87"/>
         <v>75803</v>
       </c>
-      <c r="V72" s="83">
-        <f t="shared" si="85"/>
+      <c r="V72" s="77">
+        <f t="shared" si="87"/>
         <v>78717</v>
       </c>
-      <c r="W72" s="83">
-        <f t="shared" si="85"/>
+      <c r="W72" s="77">
+        <f t="shared" si="87"/>
         <v>82166</v>
       </c>
-      <c r="X72" s="83">
+      <c r="X72" s="77">
         <f>+X70+X71</f>
         <v>81611</v>
       </c>
-      <c r="Y72" s="83">
+      <c r="Y72" s="77">
         <f>+Y70+Y71</f>
         <v>80173</v>
       </c>
@@ -7494,35 +7507,35 @@
       <c r="N74" s="3"/>
       <c r="O74" s="3"/>
       <c r="P74" s="17">
-        <f t="shared" ref="P74:W74" si="86">+P32</f>
+        <f t="shared" ref="P74:W74" si="88">+P32</f>
         <v>1401</v>
       </c>
       <c r="Q74" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>1795</v>
       </c>
       <c r="R74" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>2057</v>
       </c>
       <c r="S74" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>2459</v>
       </c>
       <c r="T74" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>4202</v>
       </c>
       <c r="U74" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>4169</v>
       </c>
       <c r="V74" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>2419</v>
       </c>
       <c r="W74" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>4246</v>
       </c>
       <c r="X74" s="17">
@@ -8283,35 +8296,35 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="17">
-        <f t="shared" ref="P90:S90" si="87">+SUM(P85:P89)</f>
+        <f t="shared" ref="P90:S90" si="89">+SUM(P85:P89)</f>
         <v>-481</v>
       </c>
       <c r="Q90" s="17">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>-581</v>
       </c>
       <c r="R90" s="17">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>622</v>
       </c>
       <c r="S90" s="17">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>-1075</v>
       </c>
       <c r="T90" s="17">
-        <f t="shared" ref="T90" si="88">+SUM(T85:T89)</f>
+        <f t="shared" ref="T90" si="90">+SUM(T85:T89)</f>
         <v>-952</v>
       </c>
       <c r="U90" s="17">
-        <f t="shared" ref="U90:W90" si="89">+SUM(U85:U89)</f>
+        <f t="shared" ref="U90:W90" si="91">+SUM(U85:U89)</f>
         <v>-1102</v>
       </c>
       <c r="V90" s="17">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>-454</v>
       </c>
       <c r="W90" s="17">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>-1314</v>
       </c>
       <c r="X90" s="17">
@@ -8340,43 +8353,43 @@
       <c r="M91" s="3"/>
       <c r="N91" s="3"/>
       <c r="O91" s="3"/>
-      <c r="P91" s="83">
-        <f t="shared" ref="P91:W91" si="90">+SUM(P74:P84)+P90</f>
+      <c r="P91" s="77">
+        <f t="shared" ref="P91:W91" si="92">+SUM(P74:P84)+P90</f>
         <v>3158</v>
       </c>
-      <c r="Q91" s="83">
-        <f t="shared" si="90"/>
+      <c r="Q91" s="77">
+        <f t="shared" si="92"/>
         <v>2531</v>
       </c>
-      <c r="R91" s="83">
-        <f t="shared" si="90"/>
+      <c r="R91" s="77">
+        <f t="shared" si="92"/>
         <v>5483</v>
       </c>
-      <c r="S91" s="83">
-        <f t="shared" si="90"/>
+      <c r="S91" s="77">
+        <f t="shared" si="92"/>
         <v>4071</v>
       </c>
-      <c r="T91" s="83">
-        <f t="shared" si="90"/>
+      <c r="T91" s="77">
+        <f t="shared" si="92"/>
         <v>5854</v>
       </c>
-      <c r="U91" s="83">
-        <f t="shared" si="90"/>
+      <c r="U91" s="77">
+        <f t="shared" si="92"/>
         <v>6340</v>
       </c>
-      <c r="V91" s="83">
-        <f t="shared" si="90"/>
+      <c r="V91" s="77">
+        <f t="shared" si="92"/>
         <v>5813</v>
       </c>
-      <c r="W91" s="83">
-        <f t="shared" si="90"/>
+      <c r="W91" s="77">
+        <f t="shared" si="92"/>
         <v>4843</v>
       </c>
-      <c r="X91" s="83">
+      <c r="X91" s="77">
         <f>+SUM(X74:X84)+X90</f>
         <v>7450</v>
       </c>
-      <c r="Y91" s="83">
+      <c r="Y91" s="77">
         <f>+SUM(Y74:Y84)+Y90</f>
         <v>6416</v>
       </c>
@@ -8880,43 +8893,43 @@
       <c r="M102" s="3"/>
       <c r="N102" s="3"/>
       <c r="O102" s="3"/>
-      <c r="P102" s="83">
-        <f t="shared" ref="P102:W102" si="91">+SUM(P92:P101)</f>
+      <c r="P102" s="77">
+        <f t="shared" ref="P102:W102" si="93">+SUM(P92:P101)</f>
         <v>-5904</v>
       </c>
-      <c r="Q102" s="83">
-        <f t="shared" si="91"/>
+      <c r="Q102" s="77">
+        <f t="shared" si="93"/>
         <v>-4485</v>
       </c>
-      <c r="R102" s="83">
-        <f t="shared" si="91"/>
+      <c r="R102" s="77">
+        <f t="shared" si="93"/>
         <v>840</v>
       </c>
-      <c r="S102" s="83">
-        <f t="shared" si="91"/>
+      <c r="S102" s="77">
+        <f t="shared" si="93"/>
         <v>-5742</v>
       </c>
-      <c r="T102" s="83">
-        <f t="shared" si="91"/>
+      <c r="T102" s="77">
+        <f t="shared" si="93"/>
         <v>-16218</v>
       </c>
-      <c r="U102" s="83">
-        <f t="shared" si="91"/>
+      <c r="U102" s="77">
+        <f t="shared" si="93"/>
         <v>-5485</v>
       </c>
-      <c r="V102" s="83">
-        <f t="shared" si="91"/>
+      <c r="V102" s="77">
+        <f t="shared" si="93"/>
         <v>-3328</v>
       </c>
-      <c r="W102" s="83">
-        <f t="shared" si="91"/>
+      <c r="W102" s="77">
+        <f t="shared" si="93"/>
         <v>752</v>
       </c>
-      <c r="X102" s="83">
+      <c r="X102" s="77">
         <f>+SUM(X92:X101)</f>
         <v>1589</v>
       </c>
-      <c r="Y102" s="83">
+      <c r="Y102" s="77">
         <f>+SUM(Y92:Y101)</f>
         <v>797</v>
       </c>
@@ -9326,43 +9339,43 @@
       <c r="M111" s="3"/>
       <c r="N111" s="3"/>
       <c r="O111" s="9"/>
-      <c r="P111" s="83">
-        <f t="shared" ref="P111:W111" si="92">+SUM(P103:P110)</f>
+      <c r="P111" s="77">
+        <f t="shared" ref="P111:W111" si="94">+SUM(P103:P110)</f>
         <v>2038</v>
       </c>
-      <c r="Q111" s="83">
-        <f t="shared" si="92"/>
+      <c r="Q111" s="77">
+        <f t="shared" si="94"/>
         <v>4084</v>
       </c>
-      <c r="R111" s="83">
-        <f t="shared" si="92"/>
+      <c r="R111" s="77">
+        <f t="shared" si="94"/>
         <v>-1262</v>
       </c>
-      <c r="S111" s="83">
-        <f t="shared" si="92"/>
+      <c r="S111" s="77">
+        <f t="shared" si="94"/>
         <v>4187</v>
       </c>
-      <c r="T111" s="83">
-        <f t="shared" si="92"/>
+      <c r="T111" s="77">
+        <f t="shared" si="94"/>
         <v>12492</v>
       </c>
-      <c r="U111" s="83">
-        <f t="shared" si="92"/>
+      <c r="U111" s="77">
+        <f t="shared" si="94"/>
         <v>-764</v>
       </c>
-      <c r="V111" s="83">
-        <f t="shared" si="92"/>
+      <c r="V111" s="77">
+        <f t="shared" si="94"/>
         <v>-1203</v>
       </c>
-      <c r="W111" s="83">
-        <f t="shared" si="92"/>
+      <c r="W111" s="77">
+        <f t="shared" si="94"/>
         <v>-2993</v>
       </c>
-      <c r="X111" s="83">
+      <c r="X111" s="77">
         <f>+SUM(X103:X110)</f>
         <v>-8276</v>
       </c>
-      <c r="Y111" s="83">
+      <c r="Y111" s="77">
         <f>+SUM(Y103:Y110)</f>
         <v>-5958</v>
       </c>
@@ -9432,44 +9445,44 @@
       <c r="M113" s="3"/>
       <c r="N113" s="3"/>
       <c r="O113" s="3"/>
-      <c r="P113" s="83">
-        <f t="shared" ref="P113" si="93">+SUM(P112,P111,P102,P91)</f>
+      <c r="P113" s="77">
+        <f t="shared" ref="P113" si="95">+SUM(P112,P111,P102,P91)</f>
         <v>-708</v>
       </c>
-      <c r="Q113" s="83">
-        <f t="shared" ref="Q113" si="94">+SUM(Q112,Q111,Q102,Q91)</f>
+      <c r="Q113" s="77">
+        <f t="shared" ref="Q113" si="96">+SUM(Q112,Q111,Q102,Q91)</f>
         <v>2166</v>
       </c>
-      <c r="R113" s="83">
-        <f t="shared" ref="R113" si="95">+SUM(R112,R111,R102,R91)</f>
+      <c r="R113" s="77">
+        <f t="shared" ref="R113" si="97">+SUM(R112,R111,R102,R91)</f>
         <v>4948</v>
       </c>
-      <c r="S113" s="83">
-        <f t="shared" ref="S113:Y113" si="96">+SUM(S112,S111,S102,S91)</f>
+      <c r="S113" s="77">
+        <f t="shared" ref="S113:Y113" si="98">+SUM(S112,S111,S102,S91)</f>
         <v>2510</v>
       </c>
-      <c r="T113" s="83">
-        <f t="shared" si="96"/>
+      <c r="T113" s="77">
+        <f t="shared" si="98"/>
         <v>2297</v>
       </c>
-      <c r="U113" s="83">
-        <f t="shared" si="96"/>
+      <c r="U113" s="77">
+        <f t="shared" si="98"/>
         <v>-11</v>
       </c>
-      <c r="V113" s="83">
-        <f t="shared" si="96"/>
+      <c r="V113" s="77">
+        <f t="shared" si="98"/>
         <v>1127</v>
       </c>
-      <c r="W113" s="83">
-        <f t="shared" si="96"/>
+      <c r="W113" s="77">
+        <f t="shared" si="98"/>
         <v>2678</v>
       </c>
-      <c r="X113" s="83">
-        <f t="shared" si="96"/>
+      <c r="X113" s="77">
+        <f t="shared" si="98"/>
         <v>556</v>
       </c>
-      <c r="Y113" s="83">
-        <f t="shared" si="96"/>
+      <c r="Y113" s="77">
+        <f t="shared" si="98"/>
         <v>1528</v>
       </c>
     </row>
@@ -9491,35 +9504,35 @@
       <c r="N114" s="3"/>
       <c r="O114" s="3"/>
       <c r="P114" s="17">
-        <f t="shared" ref="P114:W114" si="97">+P115-P113</f>
+        <f t="shared" ref="P114:W114" si="99">+P115-P113</f>
         <v>6827</v>
       </c>
       <c r="Q114" s="17">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>6119</v>
       </c>
       <c r="R114" s="17">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>8285</v>
       </c>
       <c r="S114" s="17">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>13233</v>
       </c>
       <c r="T114" s="17">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>15743</v>
       </c>
       <c r="U114" s="17">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>18040</v>
       </c>
       <c r="V114" s="17">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>18029</v>
       </c>
       <c r="W114" s="17">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>19156</v>
       </c>
       <c r="X114" s="17">
@@ -9547,35 +9560,35 @@
       <c r="N115" s="3"/>
       <c r="O115" s="3"/>
       <c r="P115" s="17">
-        <f t="shared" ref="P115:W115" si="98">+Q114</f>
+        <f t="shared" ref="P115:W115" si="100">+Q114</f>
         <v>6119</v>
       </c>
       <c r="Q115" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>8285</v>
       </c>
       <c r="R115" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>13233</v>
       </c>
       <c r="S115" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>15743</v>
       </c>
       <c r="T115" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>18040</v>
       </c>
       <c r="U115" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>18029</v>
       </c>
       <c r="V115" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>19156</v>
       </c>
       <c r="W115" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>21834</v>
       </c>
       <c r="X115" s="17">
@@ -12388,14 +12401,14 @@
       </c>
       <c r="E4" s="34">
         <f ca="1">+TODAY()</f>
-        <v>46056</v>
+        <v>46077</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>145</v>
       </c>
       <c r="J4" s="35">
         <f ca="1">V62</f>
-        <v>90.838214888266776</v>
+        <v>90.643053384631244</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>146</v>
@@ -12417,7 +12430,7 @@
       </c>
       <c r="J5" s="37">
         <f ca="1">J4/J3-1</f>
-        <v>1.162814640196828</v>
+        <v>1.1581679377293153</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>148</v>
@@ -14001,43 +14014,43 @@
       <c r="L52" s="61"/>
       <c r="M52" s="61">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>379.35085876059071</v>
+        <v>617.64322094816009</v>
       </c>
       <c r="N52" s="61">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>4268.1224286329088</v>
+        <v>4246.7202791255168</v>
       </c>
       <c r="O52" s="61">
         <f t="shared" ref="O52:U52" ca="1" si="21">O51/(1+$E$18)^O53</f>
-        <v>4387.3449856488005</v>
+        <v>4365.3450044173724</v>
       </c>
       <c r="P52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>4495.6548532621709</v>
+        <v>4473.1117610917881</v>
       </c>
       <c r="Q52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>4435.529735493652</v>
+        <v>4413.2881357900742</v>
       </c>
       <c r="R52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>4289.7052481526689</v>
+        <v>4268.194873368735</v>
       </c>
       <c r="S52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>4138.0166752558407</v>
+        <v>4117.2669303671328</v>
       </c>
       <c r="T52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>3981.9246528340095</v>
+        <v>3961.9576185766487</v>
       </c>
       <c r="U52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>3822.791710800062</v>
+        <v>3803.6226356157854</v>
       </c>
       <c r="V52" s="62">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>3661.8748313268748</v>
+        <v>3643.5126606235103</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.2">
@@ -14046,43 +14059,43 @@
       </c>
       <c r="M53" s="23">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>9.166666666666666E-2</v>
+        <v>0.15</v>
       </c>
       <c r="N53" s="23">
         <f ca="1">M53+1</f>
-        <v>1.0916666666666666</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="O53" s="23">
         <f ca="1">N53+1</f>
-        <v>2.0916666666666668</v>
+        <v>2.15</v>
       </c>
       <c r="P53" s="23">
         <f t="shared" ref="P53:V53" ca="1" si="22">O53+1</f>
-        <v>3.0916666666666668</v>
+        <v>3.15</v>
       </c>
       <c r="Q53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>4.0916666666666668</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="R53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>5.0916666666666668</v>
+        <v>5.15</v>
       </c>
       <c r="S53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>6.0916666666666668</v>
+        <v>6.15</v>
       </c>
       <c r="T53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>7.0916666666666668</v>
+        <v>7.15</v>
       </c>
       <c r="U53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>8.0916666666666668</v>
+        <v>8.15</v>
       </c>
       <c r="V53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>9.0916666666666668</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -14095,7 +14108,7 @@
       <c r="Q54" s="24"/>
       <c r="V54" s="17">
         <f ca="1">SUM(M52:V52)</f>
-        <v>37860.315980167579</v>
+        <v>37910.663119924728</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.2">
@@ -14139,7 +14152,7 @@
       <c r="U56" s="63"/>
       <c r="V56" s="64">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>46275.062080808792</v>
+        <v>46043.019581166962</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.2">
@@ -14167,7 +14180,7 @@
       <c r="U57" s="65"/>
       <c r="V57" s="66">
         <f ca="1">V54+V56</f>
-        <v>84135.378060976363</v>
+        <v>83953.68270109169</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.2">
@@ -14221,7 +14234,7 @@
       <c r="Q60" s="24"/>
       <c r="V60" s="67">
         <f ca="1">V57+V58-V59</f>
-        <v>84570.378060976363</v>
+        <v>84388.68270109169</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.2">
@@ -14258,7 +14271,7 @@
       </c>
       <c r="V62" s="67">
         <f ca="1">V60/V61</f>
-        <v>90.838214888266776</v>
+        <v>90.643053384631244</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.2">
@@ -14291,35 +14304,35 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B68" s="68"/>
-      <c r="C68" s="75" t="s">
+      <c r="C68" s="78" t="s">
         <v>162</v>
       </c>
-      <c r="D68" s="75"/>
-      <c r="E68" s="75"/>
-      <c r="F68" s="75"/>
-      <c r="G68" s="75"/>
-      <c r="H68" s="75"/>
-      <c r="I68" s="75"/>
-      <c r="J68" s="76"/>
+      <c r="D68" s="78"/>
+      <c r="E68" s="78"/>
+      <c r="F68" s="78"/>
+      <c r="G68" s="78"/>
+      <c r="H68" s="78"/>
+      <c r="I68" s="78"/>
+      <c r="J68" s="79"/>
       <c r="M68" s="68"/>
-      <c r="N68" s="77" t="s">
+      <c r="N68" s="80" t="s">
         <v>190</v>
       </c>
-      <c r="O68" s="77"/>
-      <c r="P68" s="77"/>
-      <c r="Q68" s="77"/>
-      <c r="R68" s="77"/>
-      <c r="S68" s="77"/>
-      <c r="T68" s="77"/>
-      <c r="U68" s="78"/>
+      <c r="O68" s="80"/>
+      <c r="P68" s="80"/>
+      <c r="Q68" s="80"/>
+      <c r="R68" s="80"/>
+      <c r="S68" s="80"/>
+      <c r="T68" s="80"/>
+      <c r="U68" s="81"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B69" s="79" t="s">
+      <c r="B69" s="82" t="s">
         <v>160</v>
       </c>
       <c r="C69" s="69">
         <f ca="1">+J4</f>
-        <v>90.838214888266776</v>
+        <v>90.643053384631244</v>
       </c>
       <c r="D69" s="70">
         <v>0.01</v>
@@ -14342,12 +14355,12 @@
       <c r="J69" s="70">
         <v>0.04</v>
       </c>
-      <c r="M69" s="79" t="s">
+      <c r="M69" s="82" t="s">
         <v>160</v>
       </c>
       <c r="N69" s="69">
         <f ca="1">+J4</f>
-        <v>90.838214888266776</v>
+        <v>90.643053384631244</v>
       </c>
       <c r="O69" s="70">
         <v>7.0000000000000007E-2</v>
@@ -14372,369 +14385,369 @@
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B70" s="79"/>
+      <c r="B70" s="82"/>
       <c r="C70" s="71">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D70" s="72">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>110.68087357835867</v>
+        <v>110.47542727543498</v>
       </c>
       <c r="E70" s="72">
-        <v>112.56167512018003</v>
+        <v>112.34831098314837</v>
       </c>
       <c r="F70" s="72">
-        <v>114.74110477771779</v>
+        <v>114.51856563625607</v>
       </c>
       <c r="G70" s="73">
-        <v>117.30875098568691</v>
+        <v>117.07540251837631</v>
       </c>
       <c r="H70" s="72">
-        <v>120.39401926089775</v>
+        <v>120.14768237251323</v>
       </c>
       <c r="I70" s="72">
-        <v>124.19101787856607</v>
+        <v>123.92869631317319</v>
       </c>
       <c r="J70" s="72">
-        <v>129.00477412831648</v>
-      </c>
-      <c r="M70" s="79"/>
+        <v>128.72218752029465</v>
+      </c>
+      <c r="M70" s="82"/>
       <c r="N70" s="71">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="O70" s="72">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>106.83851192787439</v>
+        <v>106.64924127211751</v>
       </c>
       <c r="P70" s="72">
-        <v>111.20111153529628</v>
+        <v>110.99347512472534</v>
       </c>
       <c r="Q70" s="72">
-        <v>114.59424456329108</v>
+        <v>114.37232367675364</v>
       </c>
       <c r="R70" s="73">
-        <v>117.30875098568691</v>
+        <v>117.07540251837631</v>
       </c>
       <c r="S70" s="72">
-        <v>119.52971078582895</v>
+        <v>119.28701247970392</v>
       </c>
       <c r="T70" s="72">
-        <v>121.38051061928067</v>
+        <v>121.13002078081027</v>
       </c>
       <c r="U70" s="72">
-        <v>122.9465720168167</v>
+        <v>122.68948934328485</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B71" s="79"/>
+      <c r="B71" s="82"/>
       <c r="C71" s="71">
         <v>0.08</v>
       </c>
       <c r="D71" s="72">
-        <v>102.36816564284882</v>
+        <v>102.17007084307576</v>
       </c>
       <c r="E71" s="72">
-        <v>103.68141578945871</v>
+        <v>103.47743850654234</v>
       </c>
       <c r="F71" s="72">
-        <v>105.1754575432501</v>
+        <v>104.96478795159516</v>
       </c>
       <c r="G71" s="73">
-        <v>106.89959770618154</v>
+        <v>106.68120511866678</v>
       </c>
       <c r="H71" s="72">
-        <v>108.92286580099504</v>
+        <v>108.69541032436288</v>
       </c>
       <c r="I71" s="72">
-        <v>111.34497113831799</v>
+        <v>111.10666624822495</v>
       </c>
       <c r="J71" s="72">
-        <v>114.31547768409148</v>
-      </c>
-      <c r="M71" s="79"/>
+        <v>114.06386690956525</v>
+      </c>
+      <c r="M71" s="82"/>
       <c r="N71" s="71">
         <v>0.08</v>
       </c>
       <c r="O71" s="72">
-        <v>97.774415260374028</v>
+        <v>97.596897392771311</v>
       </c>
       <c r="P71" s="72">
-        <v>101.57657461279382</v>
+        <v>101.38202561189443</v>
       </c>
       <c r="Q71" s="72">
-        <v>104.53380966467589</v>
+        <v>104.32601422676797</v>
       </c>
       <c r="R71" s="73">
-        <v>106.89959770618154</v>
+        <v>106.68120511866678</v>
       </c>
       <c r="S71" s="72">
-        <v>108.83524246741342</v>
+        <v>108.60817948476581</v>
       </c>
       <c r="T71" s="72">
-        <v>110.44827976844002</v>
+        <v>110.21399145651502</v>
       </c>
       <c r="U71" s="72">
-        <v>111.81315748469328</v>
+        <v>111.57275543261051</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B72" s="79"/>
+      <c r="B72" s="82"/>
       <c r="C72" s="71">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="D72" s="73">
-        <v>95.1732878159916</v>
+        <v>94.981842592068176</v>
       </c>
       <c r="E72" s="73">
-        <v>96.071612414767699</v>
+        <v>95.875902370313113</v>
       </c>
       <c r="F72" s="73">
-        <v>97.0744325578667</v>
+        <v>96.873961597434587</v>
       </c>
       <c r="G72" s="73">
-        <v>98.207872131369371</v>
+        <v>98.002020135651691</v>
       </c>
       <c r="H72" s="73">
-        <v>99.507554616294854</v>
+        <v>99.295532342535978</v>
       </c>
       <c r="I72" s="73">
-        <v>101.02335288607003</v>
+        <v>100.80413431868763</v>
       </c>
       <c r="J72" s="73">
-        <v>102.82730553564478</v>
-      </c>
-      <c r="M72" s="79"/>
+        <v>102.59952265386244</v>
+      </c>
+      <c r="M72" s="82"/>
       <c r="N72" s="71">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="O72" s="73">
-        <v>90.187116785154302</v>
+        <v>90.019343544179023</v>
       </c>
       <c r="P72" s="73">
-        <v>93.529098179410582</v>
+        <v>93.345458790625955</v>
       </c>
       <c r="Q72" s="73">
-        <v>96.128417041609907</v>
+        <v>95.932437315640243</v>
       </c>
       <c r="R72" s="73">
-        <v>98.207872131369371</v>
+        <v>98.002020135651691</v>
       </c>
       <c r="S72" s="73">
-        <v>99.909244477536205</v>
+        <v>99.695315170206484</v>
       </c>
       <c r="T72" s="73">
-        <v>101.32705476600856</v>
+        <v>101.10639436566882</v>
       </c>
       <c r="U72" s="73">
-        <v>102.52674039471594</v>
+        <v>102.30038445413696</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B73" s="79"/>
+      <c r="B73" s="82"/>
       <c r="C73" s="71">
         <v>0.09</v>
       </c>
       <c r="D73" s="72">
-        <v>88.886396755388347</v>
+        <v>88.701022483536718</v>
       </c>
       <c r="E73" s="72">
-        <v>89.478273144337138</v>
+        <v>89.289930956925915</v>
       </c>
       <c r="F73" s="72">
-        <v>90.12468421324823</v>
+        <v>89.933100650602015</v>
       </c>
       <c r="G73" s="73">
-        <v>90.838214888266776</v>
+        <v>90.643053384631244</v>
       </c>
       <c r="H73" s="72">
-        <v>91.635645070919651</v>
+        <v>91.436484919101886</v>
       </c>
       <c r="I73" s="72">
-        <v>92.539856445107148</v>
+        <v>92.33616219958887</v>
       </c>
       <c r="J73" s="72">
-        <v>93.582883368289615</v>
-      </c>
-      <c r="M73" s="79"/>
+        <v>93.373958949897073</v>
+      </c>
+      <c r="M73" s="82"/>
       <c r="N73" s="71">
         <v>0.09</v>
       </c>
       <c r="O73" s="72">
-        <v>83.737545549489909</v>
+        <v>83.577989769291833</v>
       </c>
       <c r="P73" s="72">
-        <v>86.696157773980275</v>
+        <v>86.521766275683234</v>
       </c>
       <c r="Q73" s="72">
-        <v>88.997300615250552</v>
+        <v>88.811370225098798</v>
       </c>
       <c r="R73" s="73">
-        <v>90.838214888266776</v>
+        <v>90.643053384631244</v>
       </c>
       <c r="S73" s="72">
-        <v>92.344417475280039</v>
+        <v>92.141703242430523</v>
       </c>
       <c r="T73" s="72">
-        <v>93.59958629779112</v>
+        <v>93.390578123929913</v>
       </c>
       <c r="U73" s="72">
-        <v>94.661652224531238</v>
+        <v>94.447318408275549</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B74" s="79"/>
+      <c r="B74" s="82"/>
       <c r="C74" s="71">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="D74" s="72">
-        <v>83.347031492880021</v>
+        <v>83.167244146221094</v>
       </c>
       <c r="E74" s="72">
-        <v>83.710894043584574</v>
+        <v>83.529185496844093</v>
       </c>
       <c r="F74" s="72">
-        <v>84.09639567062429</v>
+        <v>83.912651669133467</v>
       </c>
       <c r="G74" s="73">
-        <v>84.508173318928158</v>
+        <v>84.322255124874872</v>
       </c>
       <c r="H74" s="72">
-        <v>84.952290685710977</v>
+        <v>84.764027544864945</v>
       </c>
       <c r="I74" s="72">
-        <v>85.436832700592475</v>
+        <v>85.246011170165801</v>
       </c>
       <c r="J74" s="72">
-        <v>85.972824267599577</v>
-      </c>
-      <c r="M74" s="79"/>
+        <v>85.77917269313501</v>
+      </c>
+      <c r="M74" s="82"/>
       <c r="N74" s="71">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="O74" s="72">
-        <v>78.183416732842318</v>
+        <v>78.030893354620986</v>
       </c>
       <c r="P74" s="72">
-        <v>80.818731977044763</v>
+        <v>80.652294092226768</v>
       </c>
       <c r="Q74" s="72">
-        <v>82.868421611424438</v>
+        <v>82.69116133258683</v>
       </c>
       <c r="R74" s="73">
-        <v>84.508173318928158</v>
+        <v>84.322255124874872</v>
       </c>
       <c r="S74" s="72">
-        <v>85.849788352340298</v>
+        <v>85.656786409474194</v>
       </c>
       <c r="T74" s="72">
-        <v>86.967800880183759</v>
+        <v>86.768895813306941</v>
       </c>
       <c r="U74" s="72">
-        <v>87.913811480666695</v>
+        <v>87.7099114627039</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="79"/>
+      <c r="B75" s="82"/>
       <c r="C75" s="71">
         <v>0.1</v>
       </c>
       <c r="D75" s="72">
-        <v>78.430395878282539</v>
+        <v>78.255785281906597</v>
       </c>
       <c r="E75" s="72">
-        <v>78.623786900575539</v>
+        <v>78.448104079852257</v>
       </c>
       <c r="F75" s="72">
-        <v>78.817177922868566</v>
+        <v>78.640422877797917</v>
       </c>
       <c r="G75" s="73">
-        <v>79.010568945161552</v>
+        <v>78.832741675743563</v>
       </c>
       <c r="H75" s="72">
-        <v>79.203959967454566</v>
+        <v>79.025060473689209</v>
       </c>
       <c r="I75" s="72">
-        <v>79.397350989747579</v>
+        <v>79.217379271634854</v>
       </c>
       <c r="J75" s="72">
-        <v>79.590742012040579</v>
-      </c>
-      <c r="M75" s="79"/>
+        <v>79.409698069580529</v>
+      </c>
+      <c r="M75" s="82"/>
       <c r="N75" s="71">
         <v>0.1</v>
       </c>
       <c r="O75" s="72">
-        <v>73.346974720866356</v>
+        <v>73.200548307335254</v>
       </c>
       <c r="P75" s="72">
-        <v>75.706805647656012</v>
+        <v>75.547295544172059</v>
       </c>
       <c r="Q75" s="72">
-        <v>77.542229701825775</v>
+        <v>77.372543395045128</v>
       </c>
       <c r="R75" s="73">
-        <v>79.010568945161552</v>
+        <v>78.832741675743563</v>
       </c>
       <c r="S75" s="72">
-        <v>80.211937416981755</v>
+        <v>80.02744935995139</v>
       </c>
       <c r="T75" s="72">
-        <v>81.213077810165245</v>
+        <v>81.023039096791237</v>
       </c>
       <c r="U75" s="72">
-        <v>82.060196604397433</v>
+        <v>81.865461181809565</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B76" s="80"/>
+      <c r="B76" s="83"/>
       <c r="C76" s="71">
         <v>0.105</v>
       </c>
       <c r="D76" s="72">
-        <v>74.037972889261155</v>
+        <v>73.868187423289683</v>
       </c>
       <c r="E76" s="72">
-        <v>74.10363104679837</v>
+        <v>73.933464278772945</v>
       </c>
       <c r="F76" s="72">
-        <v>74.155180839906095</v>
+        <v>73.984714702499502</v>
       </c>
       <c r="G76" s="73">
-        <v>74.189976950253836</v>
+        <v>74.019308738514908</v>
       </c>
       <c r="H76" s="72">
-        <v>74.20466864128953</v>
+        <v>74.033915109276975</v>
       </c>
       <c r="I76" s="72">
-        <v>74.194947823160632</v>
+        <v>74.024250743659962</v>
       </c>
       <c r="J76" s="72">
-        <v>74.155180839906095</v>
-      </c>
-      <c r="M76" s="80"/>
+        <v>73.984714702499502</v>
+      </c>
+      <c r="M76" s="83"/>
       <c r="N76" s="71">
         <v>0.105</v>
       </c>
       <c r="O76" s="72">
-        <v>69.094832220766278</v>
+        <v>68.953753464828992</v>
       </c>
       <c r="P76" s="72">
-        <v>71.217809191386081</v>
+        <v>71.064401495531456</v>
       </c>
       <c r="Q76" s="72">
-        <v>72.869013501868167</v>
+        <v>72.706016630522271</v>
       </c>
       <c r="R76" s="73">
-        <v>74.189976950253836</v>
+        <v>74.019308738514908</v>
       </c>
       <c r="S76" s="72">
-        <v>75.270765226205725</v>
+        <v>75.09382046323617</v>
       </c>
       <c r="T76" s="72">
-        <v>76.171422122832311</v>
+        <v>75.989246900503886</v>
       </c>
       <c r="U76" s="72">
-        <v>76.933516419977892</v>
+        <v>76.746915424345801</v>
       </c>
     </row>
   </sheetData>

--- a/PYPL.xlsx
+++ b/PYPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA842752-6BD9-4133-8C2B-10139E26A19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC06EC8-AC44-4368-84BD-1D9AECC834EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{B690896D-DF4D-4BA1-A25A-CD8C19559281}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B690896D-DF4D-4BA1-A25A-CD8C19559281}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1573,6 +1573,10 @@
     </xf>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1591,10 +1595,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="I2" s="2">
-        <v>45.76</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -2106,7 +2106,7 @@
       <c r="I3" s="3">
         <v>882.10549300000002</v>
       </c>
-      <c r="J3" s="85" t="s">
+      <c r="J3" s="79" t="s">
         <v>342</v>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I3*I2</f>
-        <v>40365.147359679999</v>
+        <v>48824.539037549999</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -2133,7 +2133,7 @@
         <f>6977+2365</f>
         <v>9342</v>
       </c>
-      <c r="J5" s="85" t="s">
+      <c r="J5" s="79" t="s">
         <v>342</v>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       <c r="I6" s="3">
         <v>9409</v>
       </c>
-      <c r="J6" s="85" t="s">
+      <c r="J6" s="79" t="s">
         <v>342</v>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>40432.147359679999</v>
+        <v>48891.539037549999</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -2296,7 +2296,7 @@
       <c r="I23" s="3"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="86" t="s">
+      <c r="B24" s="80" t="s">
         <v>346</v>
       </c>
     </row>
@@ -2369,16 +2369,16 @@
       <c r="N2" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="O2" s="85" t="s">
+      <c r="O2" s="79" t="s">
         <v>342</v>
       </c>
-      <c r="P2" s="85" t="s">
+      <c r="P2" s="79" t="s">
         <v>343</v>
       </c>
-      <c r="Q2" s="85" t="s">
+      <c r="Q2" s="79" t="s">
         <v>344</v>
       </c>
-      <c r="R2" s="85" t="s">
+      <c r="R2" s="79" t="s">
         <v>345</v>
       </c>
       <c r="S2" s="4"/>
@@ -3293,27 +3293,27 @@
         <v>1.8566584879365702E-2</v>
       </c>
       <c r="J13" s="10">
-        <f>+J19/J12</f>
+        <f t="shared" ref="J13:O13" si="19">+J19/J12</f>
         <v>1.9107611068984735E-2</v>
       </c>
       <c r="K13" s="10">
-        <f>+K19/K12</f>
+        <f t="shared" si="19"/>
         <v>1.8674138559183907E-2</v>
       </c>
       <c r="L13" s="10">
-        <f>+L19/L12</f>
+        <f t="shared" si="19"/>
         <v>1.8685731162650182E-2</v>
       </c>
       <c r="M13" s="10">
-        <f>+M19/M12</f>
+        <f t="shared" si="19"/>
         <v>1.8374198843890258E-2</v>
       </c>
       <c r="N13" s="10">
-        <f>+N19/N12</f>
+        <f t="shared" si="19"/>
         <v>1.826007345280815E-2</v>
       </c>
       <c r="O13" s="10">
-        <f>+O19/O12</f>
+        <f t="shared" si="19"/>
         <v>1.8003901240422025E-2</v>
       </c>
       <c r="P13" s="10"/>
@@ -3321,43 +3321,43 @@
       <c r="R13" s="10"/>
       <c r="S13" s="11"/>
       <c r="T13" s="10">
-        <f t="shared" ref="T13:V13" si="19">+T19/T12</f>
+        <f t="shared" ref="T13:V13" si="20">+T19/T12</f>
         <v>3.012269120490765E-2</v>
       </c>
       <c r="U13" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.8703644841169804E-2</v>
       </c>
       <c r="V13" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.6712469680283669E-2</v>
       </c>
       <c r="W13" s="10">
-        <f t="shared" ref="W13:AC13" si="20">+W19/W12</f>
+        <f t="shared" ref="W13:AC13" si="21">+W19/W12</f>
         <v>2.4963303718790603E-2</v>
       </c>
       <c r="X13" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.2919422004098019E-2</v>
       </c>
       <c r="Y13" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.0363935823623322E-2</v>
       </c>
       <c r="Z13" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.0276882084897932E-2</v>
       </c>
       <c r="AA13" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.9476258668999116E-2</v>
       </c>
       <c r="AB13" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.8913838741337775E-2</v>
       </c>
       <c r="AC13" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.8490740415579E-2</v>
       </c>
       <c r="AD13" s="11"/>
@@ -3583,7 +3583,7 @@
         <v>13530</v>
       </c>
       <c r="AC16" s="3">
-        <f t="shared" ref="AC16:AC18" si="21">+SUM(K16:N16)</f>
+        <f t="shared" ref="AC16:AC18" si="22">+SUM(K16:N16)</f>
         <v>14304</v>
       </c>
       <c r="AD16" s="3"/>
@@ -3673,7 +3673,7 @@
         <v>28842</v>
       </c>
       <c r="AC17" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29798</v>
       </c>
       <c r="AD17" s="3"/>
@@ -3763,7 +3763,7 @@
         <v>2955</v>
       </c>
       <c r="AC18" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3374</v>
       </c>
       <c r="AD18" s="3"/>
@@ -4085,55 +4085,55 @@
         <v>28</v>
       </c>
       <c r="C22" s="3">
-        <f t="shared" ref="C22" si="22">+C19-SUM(C20:C21)</f>
+        <f t="shared" ref="C22" si="23">+C19-SUM(C20:C21)</f>
         <v>3315</v>
       </c>
       <c r="D22" s="3">
-        <f t="shared" ref="D22" si="23">+D19-SUM(D20:D21)</f>
+        <f t="shared" ref="D22" si="24">+D19-SUM(D20:D21)</f>
         <v>3348</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" ref="E22" si="24">+E19-SUM(E20:E21)</f>
+        <f t="shared" ref="E22" si="25">+E19-SUM(E20:E21)</f>
         <v>3369</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" ref="F22" si="25">+F19-SUM(F20:F21)</f>
+        <f t="shared" ref="F22" si="26">+F19-SUM(F20:F21)</f>
         <v>3672</v>
       </c>
       <c r="G22" s="3">
-        <f t="shared" ref="G22" si="26">+G19-SUM(G20:G21)</f>
+        <f t="shared" ref="G22" si="27">+G19-SUM(G20:G21)</f>
         <v>3461</v>
       </c>
       <c r="H22" s="3">
-        <f t="shared" ref="H22" si="27">+H19-SUM(H20:H21)</f>
+        <f t="shared" ref="H22" si="28">+H19-SUM(H20:H21)</f>
         <v>3608</v>
       </c>
       <c r="I22" s="3">
-        <f t="shared" ref="I22" si="28">+I19-SUM(I20:I21)</f>
+        <f t="shared" ref="I22" si="29">+I19-SUM(I20:I21)</f>
         <v>3654</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" ref="J22:O22" si="29">+J19-SUM(J20:J21)</f>
+        <f t="shared" ref="J22:O22" si="30">+J19-SUM(J20:J21)</f>
         <v>3935</v>
       </c>
       <c r="K22" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3716</v>
       </c>
       <c r="L22" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3844</v>
       </c>
       <c r="M22" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3871</v>
       </c>
       <c r="N22" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>4034</v>
       </c>
       <c r="O22" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3810</v>
       </c>
       <c r="P22" s="3"/>
@@ -4141,35 +4141,35 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3">
-        <f t="shared" ref="T22:U22" si="30">+T19-SUM(T20:T21)</f>
+        <f t="shared" ref="T22:U22" si="31">+T19-SUM(T20:T21)</f>
         <v>5684</v>
       </c>
       <c r="U22" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6859</v>
       </c>
       <c r="V22" s="3">
-        <f t="shared" ref="V22:AA22" si="31">+V19-SUM(V20:V21)</f>
+        <f t="shared" ref="V22:AA22" si="32">+V19-SUM(V20:V21)</f>
         <v>7820</v>
       </c>
       <c r="W22" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9602</v>
       </c>
       <c r="X22" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>11779</v>
       </c>
       <c r="Y22" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>13996</v>
       </c>
       <c r="Z22" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>13773</v>
       </c>
       <c r="AA22" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>13704</v>
       </c>
       <c r="AB22" s="3">
@@ -4690,35 +4690,35 @@
         <v>35</v>
       </c>
       <c r="C28" s="3">
-        <f t="shared" ref="C28" si="32">+C22-SUM(C23:C27)</f>
+        <f t="shared" ref="C28" si="33">+C22-SUM(C23:C27)</f>
         <v>999</v>
       </c>
       <c r="D28" s="3">
-        <f t="shared" ref="D28" si="33">+D22-SUM(D23:D27)</f>
+        <f t="shared" ref="D28" si="34">+D22-SUM(D23:D27)</f>
         <v>1133</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" ref="E28" si="34">+E22-SUM(E23:E27)</f>
+        <f t="shared" ref="E28" si="35">+E22-SUM(E23:E27)</f>
         <v>1168</v>
       </c>
       <c r="F28" s="3">
-        <f t="shared" ref="F28" si="35">+F22-SUM(F23:F27)</f>
+        <f t="shared" ref="F28" si="36">+F22-SUM(F23:F27)</f>
         <v>1728</v>
       </c>
       <c r="G28" s="3">
-        <f t="shared" ref="G28" si="36">+G22-SUM(G23:G27)</f>
+        <f t="shared" ref="G28" si="37">+G22-SUM(G23:G27)</f>
         <v>1168</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" ref="H28" si="37">+H22-SUM(H23:H27)</f>
+        <f t="shared" ref="H28" si="38">+H22-SUM(H23:H27)</f>
         <v>1325</v>
       </c>
       <c r="I28" s="3">
-        <f t="shared" ref="I28" si="38">+I22-SUM(I23:I27)</f>
+        <f t="shared" ref="I28" si="39">+I22-SUM(I23:I27)</f>
         <v>1391</v>
       </c>
       <c r="J28" s="3">
-        <f t="shared" ref="J28" si="39">+J22-SUM(J23:J27)</f>
+        <f t="shared" ref="J28" si="40">+J22-SUM(J23:J27)</f>
         <v>1441</v>
       </c>
       <c r="K28" s="3">
@@ -4746,7 +4746,7 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3">
-        <f t="shared" ref="T28:AA28" si="40">+T22-SUM(T23:T27)</f>
+        <f t="shared" ref="T28:AA28" si="41">+T22-SUM(T23:T27)</f>
         <v>1586</v>
       </c>
       <c r="U28" s="3">
@@ -4754,27 +4754,27 @@
         <v>2127</v>
       </c>
       <c r="V28" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2194</v>
       </c>
       <c r="W28" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2719</v>
       </c>
       <c r="X28" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3289</v>
       </c>
       <c r="Y28" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4262</v>
       </c>
       <c r="Z28" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3837</v>
       </c>
       <c r="AA28" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>5028</v>
       </c>
       <c r="AB28" s="3">
@@ -4907,27 +4907,27 @@
         <v>37</v>
       </c>
       <c r="C30" s="3">
-        <f t="shared" ref="C30:H30" si="41">+C28+C29</f>
+        <f t="shared" ref="C30:H30" si="42">+C28+C29</f>
         <v>1074</v>
       </c>
       <c r="D30" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1303</v>
       </c>
       <c r="E30" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1241</v>
       </c>
       <c r="F30" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1793</v>
       </c>
       <c r="G30" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1209</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1399</v>
       </c>
       <c r="I30" s="3">
@@ -4935,15 +4935,15 @@
         <v>1311</v>
       </c>
       <c r="J30" s="3">
-        <f t="shared" ref="J30:AC30" si="42">+J28+J29</f>
+        <f t="shared" ref="J30:AC30" si="43">+J28+J29</f>
         <v>1410</v>
       </c>
       <c r="K30" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1603</v>
       </c>
       <c r="L30" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1529</v>
       </c>
       <c r="M30" s="3">
@@ -4963,43 +4963,43 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1631</v>
       </c>
       <c r="U30" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2200</v>
       </c>
       <c r="V30" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2376</v>
       </c>
       <c r="W30" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2998</v>
       </c>
       <c r="X30" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>5065</v>
       </c>
       <c r="Y30" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>4099</v>
       </c>
       <c r="Z30" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>3366</v>
       </c>
       <c r="AA30" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>5411</v>
       </c>
       <c r="AB30" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>5329</v>
       </c>
       <c r="AC30" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>6292</v>
       </c>
       <c r="AD30" s="3"/>
@@ -5124,27 +5124,27 @@
         <v>39</v>
       </c>
       <c r="C32" s="3">
-        <f t="shared" ref="C32:H32" si="43">+C30-C31</f>
+        <f t="shared" ref="C32:H32" si="44">+C30-C31</f>
         <v>795</v>
       </c>
       <c r="D32" s="3">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1029</v>
       </c>
       <c r="E32" s="3">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1020</v>
       </c>
       <c r="F32" s="3">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1402</v>
       </c>
       <c r="G32" s="3">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>888</v>
       </c>
       <c r="H32" s="3">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1128</v>
       </c>
       <c r="I32" s="3">
@@ -5152,15 +5152,15 @@
         <v>1010</v>
       </c>
       <c r="J32" s="3">
-        <f t="shared" ref="J32:L32" si="44">+J30-J31</f>
+        <f t="shared" ref="J32:L32" si="45">+J30-J31</f>
         <v>1121</v>
       </c>
       <c r="K32" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1287</v>
       </c>
       <c r="L32" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1260</v>
       </c>
       <c r="M32" s="3">
@@ -5180,27 +5180,27 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3">
-        <f t="shared" ref="T32:Y32" si="45">+T30-T31</f>
+        <f t="shared" ref="T32:Y32" si="46">+T30-T31</f>
         <v>1401</v>
       </c>
       <c r="U32" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1795</v>
       </c>
       <c r="V32" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2057</v>
       </c>
       <c r="W32" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2459</v>
       </c>
       <c r="X32" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>4202</v>
       </c>
       <c r="Y32" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>4169</v>
       </c>
       <c r="Z32" s="3">
@@ -5208,15 +5208,15 @@
         <v>2419</v>
       </c>
       <c r="AA32" s="3">
-        <f t="shared" ref="AA32:AC32" si="46">+AA30-AA31</f>
+        <f t="shared" ref="AA32:AC32" si="47">+AA30-AA31</f>
         <v>4246</v>
       </c>
       <c r="AB32" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>4147</v>
       </c>
       <c r="AC32" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>5233</v>
       </c>
       <c r="AD32" s="3"/>
@@ -5292,11 +5292,11 @@
         <v>40</v>
       </c>
       <c r="C34" s="12">
-        <f t="shared" ref="C34:D34" si="47">+C32/C35</f>
+        <f t="shared" ref="C34:D34" si="48">+C32/C35</f>
         <v>0.70416297608503098</v>
       </c>
       <c r="D34" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.9261926192619262</v>
       </c>
       <c r="E34" s="12">
@@ -5308,39 +5308,39 @@
         <v>1.3017641597028784</v>
       </c>
       <c r="G34" s="12">
-        <f t="shared" ref="G34:O34" si="48">+G32/G35</f>
+        <f t="shared" ref="G34:O34" si="49">+G32/G35</f>
         <v>0.83458646616541354</v>
       </c>
       <c r="H34" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1</v>
       </c>
       <c r="I34" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.99507389162561577</v>
       </c>
       <c r="J34" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1.1243731193580742</v>
       </c>
       <c r="K34" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1.3052738336713996</v>
       </c>
       <c r="L34" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1.3003095975232197</v>
       </c>
       <c r="M34" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1.3136842105263158</v>
       </c>
       <c r="N34" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1.543501611170784</v>
       </c>
       <c r="O34" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1.2190580503833517</v>
       </c>
       <c r="P34" s="12"/>
@@ -5348,35 +5348,35 @@
       <c r="R34" s="12"/>
       <c r="S34" s="12"/>
       <c r="T34" s="12">
-        <f t="shared" ref="T34:AA34" si="49">+T32/T35</f>
+        <f t="shared" ref="T34:AA34" si="50">+T32/T35</f>
         <v>1.1578512396694214</v>
       </c>
       <c r="U34" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>1.4921030756442228</v>
       </c>
       <c r="V34" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>1.7373310810810811</v>
       </c>
       <c r="W34" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>2.094548551959114</v>
       </c>
       <c r="X34" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>3.5822676896845693</v>
       </c>
       <c r="Y34" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>3.5511073253833048</v>
       </c>
       <c r="Z34" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>2.0889464594127807</v>
       </c>
       <c r="AA34" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>3.8355916892502258</v>
       </c>
       <c r="AB34" s="12">
@@ -5561,43 +5561,43 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="11">
-        <f t="shared" ref="G37:J37" si="50">+G7/C7-1</f>
+        <f t="shared" ref="G37:J37" si="51">+G7/C7-1</f>
         <v>-1.3856812933025431E-2</v>
       </c>
       <c r="H37" s="11">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-4.6403712296984034E-3</v>
       </c>
       <c r="I37" s="11">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>9.3457943925232545E-3</v>
       </c>
       <c r="J37" s="11">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.8779342723004744E-2</v>
       </c>
       <c r="K37" s="11">
-        <f t="shared" ref="K37:M38" si="51">+K7/G7-1</f>
+        <f t="shared" ref="K37:M38" si="52">+K7/G7-1</f>
         <v>2.1077283372365363E-2</v>
       </c>
       <c r="L37" s="11">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>2.0979020979021046E-2</v>
       </c>
       <c r="M37" s="11">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.388888888888884E-2</v>
       </c>
       <c r="N37" s="11">
-        <f t="shared" ref="N37:N38" si="52">+N7/J7-1</f>
+        <f t="shared" ref="N37:N38" si="53">+N7/J7-1</f>
         <v>1.1520737327188835E-2</v>
       </c>
       <c r="O37" s="11">
-        <f t="shared" ref="O37:O38" si="53">+O7/K7-1</f>
+        <f t="shared" ref="O37:O38" si="54">+O7/K7-1</f>
         <v>6.8807339449541427E-3</v>
       </c>
       <c r="P37" s="11">
-        <f t="shared" ref="P37:P38" si="54">+P7/L7-1</f>
+        <f t="shared" ref="P37:P38" si="55">+P7/L7-1</f>
         <v>-1</v>
       </c>
       <c r="Q37" s="3"/>
@@ -5605,39 +5605,39 @@
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="11">
-        <f t="shared" ref="U37:W37" si="55">+U7/T7-1</f>
+        <f t="shared" ref="U37:W37" si="56">+U7/T7-1</f>
         <v>0.15075376884422109</v>
       </c>
       <c r="V37" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.1659388646288209</v>
       </c>
       <c r="W37" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.14232209737827706</v>
       </c>
       <c r="X37" s="11">
-        <f t="shared" ref="X37:AC38" si="56">+X7/W7-1</f>
+        <f t="shared" ref="X37:AC38" si="57">+X7/W7-1</f>
         <v>0.23606557377049175</v>
       </c>
       <c r="Y37" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.12997347480106103</v>
       </c>
       <c r="Z37" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>2.1126760563380254E-2</v>
       </c>
       <c r="AA37" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>-2.0689655172413834E-2</v>
       </c>
       <c r="AB37" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>1.8779342723004744E-2</v>
       </c>
       <c r="AC37" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>1.1520737327188835E-2</v>
       </c>
       <c r="AD37" s="3"/>
@@ -5669,43 +5669,43 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="11">
-        <f t="shared" ref="G38:J38" si="57">+G8/C8-1</f>
+        <f t="shared" ref="G38:J38" si="58">+G8/C8-1</f>
         <v>0.11482433590402752</v>
       </c>
       <c r="H38" s="11">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>8.3305893974316758E-2</v>
       </c>
       <c r="I38" s="11">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>5.6733067729083597E-2</v>
       </c>
       <c r="J38" s="11">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>-2.6331273904089403E-2</v>
       </c>
       <c r="K38" s="11">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>-7.0714834742505728E-2</v>
       </c>
       <c r="L38" s="11">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>-5.3799392097264476E-2</v>
       </c>
       <c r="M38" s="11">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>-4.524204494043127E-2</v>
       </c>
       <c r="N38" s="11">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>2.0395830185828689E-2</v>
       </c>
       <c r="O38" s="11">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>7.1133167907361461E-2</v>
       </c>
       <c r="P38" s="11">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>-1</v>
       </c>
       <c r="Q38" s="3"/>
@@ -5713,35 +5713,35 @@
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="11">
-        <f t="shared" ref="U38:W38" si="58">+U8/T8-1</f>
+        <f t="shared" ref="U38:W38" si="59">+U8/T8-1</f>
         <v>0.23415409054805392</v>
       </c>
       <c r="V38" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.27056249195520654</v>
       </c>
       <c r="W38" s="11">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.25225407760105356</v>
       </c>
       <c r="X38" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.24771458619852771</v>
       </c>
       <c r="Y38" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.25449004733190694</v>
       </c>
       <c r="Z38" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.15510647095307006</v>
       </c>
       <c r="AA38" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.11776813280236254</v>
       </c>
       <c r="AB38" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>5.4161162483487457E-2</v>
       </c>
       <c r="AC38" s="11">
@@ -5777,43 +5777,43 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="11">
-        <f t="shared" ref="G39:M39" si="59">+G12/C12-1</f>
+        <f t="shared" ref="G39:M39" si="60">+G12/C12-1</f>
         <v>0.1392126552856352</v>
       </c>
       <c r="H39" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.10696397176380601</v>
       </c>
       <c r="I39" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>9.0120995303081486E-2</v>
       </c>
       <c r="J39" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>6.8330437837943458E-2</v>
       </c>
       <c r="K39" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>3.3051057297083242E-2</v>
       </c>
       <c r="L39" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>6.4136521326059182E-2</v>
       </c>
       <c r="M39" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>8.387023502215829E-2</v>
       </c>
       <c r="N39" s="11">
-        <f t="shared" ref="N39" si="60">+N12/J12-1</f>
+        <f t="shared" ref="N39" si="61">+N12/J12-1</f>
         <v>8.5189431659342674E-2</v>
       </c>
       <c r="O39" s="11">
-        <f t="shared" ref="O39" si="61">+O12/K12-1</f>
+        <f t="shared" ref="O39" si="62">+O12/K12-1</f>
         <v>0.11204722824106916</v>
       </c>
       <c r="P39" s="11">
-        <f t="shared" ref="P39" si="62">+P12/L12-1</f>
+        <f t="shared" ref="P39" si="63">+P12/L12-1</f>
         <v>-1</v>
       </c>
       <c r="Q39" s="11"/>
@@ -5821,39 +5821,39 @@
       <c r="S39" s="11"/>
       <c r="T39" s="11"/>
       <c r="U39" s="11">
-        <f t="shared" ref="U39:W39" si="63">+U12/T12-1</f>
+        <f t="shared" ref="U39:W39" si="64">+U12/T12-1</f>
         <v>0.26741737236336149</v>
       </c>
       <c r="V39" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.26796498742818065</v>
       </c>
       <c r="W39" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.23081192007869733</v>
       </c>
       <c r="X39" s="11">
-        <f t="shared" ref="X39:AC39" si="64">+X12/W12-1</f>
+        <f t="shared" ref="X39:AC39" si="65">+X12/W12-1</f>
         <v>0.31483232082031121</v>
       </c>
       <c r="Y39" s="11">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.33097914454384436</v>
       </c>
       <c r="Z39" s="11">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>8.9280740746091825E-2</v>
       </c>
       <c r="AA39" s="11">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.12634697799444705</v>
       </c>
       <c r="AB39" s="11">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>9.9812309340897576E-2</v>
       </c>
       <c r="AC39" s="11">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>6.711417779496176E-2</v>
       </c>
       <c r="AD39" s="11"/>
@@ -5885,43 +5885,43 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="11">
-        <f t="shared" ref="G40:M42" si="65">+G17/C17-1</f>
+        <f t="shared" ref="G40:M42" si="66">+G17/C17-1</f>
         <v>0.10527969830295403</v>
       </c>
       <c r="H40" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>1.6917827694057364E-2</v>
       </c>
       <c r="I40" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>6.2067929065223959E-2</v>
       </c>
       <c r="J40" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>4.1878346835095392E-2</v>
       </c>
       <c r="K40" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>-2.5589991470003071E-3</v>
       </c>
       <c r="L40" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>4.0262826785963934E-2</v>
       </c>
       <c r="M40" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>6.438375548323183E-2</v>
       </c>
       <c r="N40" s="11">
-        <f t="shared" ref="N40:N42" si="66">+N17/J17-1</f>
+        <f t="shared" ref="N40:N42" si="67">+N17/J17-1</f>
         <v>3.0442804428044257E-2</v>
       </c>
       <c r="O40" s="11">
-        <f t="shared" ref="O40:O42" si="67">+O17/K17-1</f>
+        <f t="shared" ref="O40:O42" si="68">+O17/K17-1</f>
         <v>6.912770809578106E-2</v>
       </c>
       <c r="P40" s="11">
-        <f t="shared" ref="P40:P42" si="68">+P17/L17-1</f>
+        <f t="shared" ref="P40:P42" si="69">+P17/L17-1</f>
         <v>-1</v>
       </c>
       <c r="Q40" s="11"/>
@@ -5929,39 +5929,39 @@
       <c r="S40" s="11"/>
       <c r="T40" s="11"/>
       <c r="U40" s="11">
-        <f t="shared" ref="U40:W40" si="69">+U17/T17-1</f>
+        <f t="shared" ref="U40:W40" si="70">+U17/T17-1</f>
         <v>0.19989567031820554</v>
       </c>
       <c r="V40" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.19198330579949574</v>
       </c>
       <c r="W40" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.17433802611423155</v>
       </c>
       <c r="X40" s="11">
-        <f t="shared" ref="X40:AC42" si="70">+X17/W17-1</f>
+        <f t="shared" ref="X40:AC42" si="71">+X17/W17-1</f>
         <v>0.23721970308714835</v>
       </c>
       <c r="Y40" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.17491716035746552</v>
       </c>
       <c r="Z40" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>7.7087428424921001E-2</v>
       </c>
       <c r="AA40" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>6.5500277711656008E-2</v>
       </c>
       <c r="AB40" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>7.3909967606210714E-2</v>
       </c>
       <c r="AC40" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>3.314610637265103E-2</v>
       </c>
       <c r="AD40" s="11"/>
@@ -5993,43 +5993,43 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>-1.6272189349112454E-2</v>
       </c>
       <c r="H41" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.10075187969924815</v>
       </c>
       <c r="I41" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>2.0942408376963373E-2</v>
       </c>
       <c r="J41" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>4.7106325706594898E-2</v>
       </c>
       <c r="K41" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.16541353383458657</v>
       </c>
       <c r="L41" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.15710382513661192</v>
       </c>
       <c r="M41" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.14743589743589736</v>
       </c>
       <c r="N41" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.10154241645244211</v>
       </c>
       <c r="O41" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>9.9354838709677429E-2</v>
       </c>
       <c r="P41" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-1</v>
       </c>
       <c r="Q41" s="11"/>
@@ -6037,39 +6037,39 @@
       <c r="S41" s="11"/>
       <c r="T41" s="11"/>
       <c r="U41" s="11">
-        <f t="shared" ref="U41:W41" si="71">+U18/T18-1</f>
+        <f t="shared" ref="U41:W41" si="72">+U18/T18-1</f>
         <v>0.26730310262529833</v>
       </c>
       <c r="V41" s="11">
+        <f t="shared" si="72"/>
+        <v>9.3534212178280063E-2</v>
+      </c>
+      <c r="W41" s="11">
+        <f t="shared" si="72"/>
+        <v>-3.960964408725598E-2</v>
+      </c>
+      <c r="X41" s="11">
         <f t="shared" si="71"/>
-        <v>9.3534212178280063E-2</v>
-      </c>
-      <c r="W41" s="11">
+        <v>-8.1888822474596501E-2</v>
+      </c>
+      <c r="Y41" s="11">
         <f t="shared" si="71"/>
-        <v>-3.960964408725598E-2</v>
-      </c>
-      <c r="X41" s="11">
-        <f t="shared" si="70"/>
-        <v>-8.1888822474596501E-2</v>
-      </c>
-      <c r="Y41" s="11">
-        <f t="shared" si="70"/>
         <v>0.28190104166666674</v>
       </c>
       <c r="Z41" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.17420010157440324</v>
       </c>
       <c r="AA41" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.26038062283737018</v>
       </c>
       <c r="AB41" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>1.4070006863418083E-2</v>
       </c>
       <c r="AC41" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.14179357021996619</v>
       </c>
       <c r="AD41" s="11"/>
@@ -6101,43 +6101,43 @@
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="13">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>9.3607954545454453E-2</v>
       </c>
       <c r="H42" s="13">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>8.2063949499108002E-2</v>
       </c>
       <c r="I42" s="13">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>5.7832299811269916E-2</v>
       </c>
       <c r="J42" s="13">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>4.2362322452030865E-2</v>
       </c>
       <c r="K42" s="13">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>1.1949603844655154E-2</v>
       </c>
       <c r="L42" s="13">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>5.1109701965757814E-2</v>
       </c>
       <c r="M42" s="13">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>7.2639225181598155E-2</v>
       </c>
       <c r="N42" s="13">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>3.7054745398039657E-2</v>
       </c>
       <c r="O42" s="13">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>7.2134514183031628E-2</v>
       </c>
       <c r="P42" s="13">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-1</v>
       </c>
       <c r="Q42" s="13"/>
@@ -6145,39 +6145,39 @@
       <c r="S42" s="11"/>
       <c r="T42" s="13"/>
       <c r="U42" s="13">
-        <f t="shared" ref="U42:W42" si="72">+U19/T19-1</f>
+        <f t="shared" ref="U42:W42" si="73">+U19/T19-1</f>
         <v>0.20771075447334431</v>
       </c>
       <c r="V42" s="13">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.18000610966855057</v>
       </c>
       <c r="W42" s="13">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.15021681444566704</v>
       </c>
       <c r="X42" s="13">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.20717983344586988</v>
       </c>
       <c r="Y42" s="13">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.18257667567819524</v>
       </c>
       <c r="Z42" s="13">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>8.4624177210200546E-2</v>
       </c>
       <c r="AA42" s="13">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>8.1873682680427384E-2</v>
       </c>
       <c r="AB42" s="13">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>6.8052803063383793E-2</v>
       </c>
       <c r="AC42" s="13">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>4.3243073245903707E-2</v>
       </c>
       <c r="AD42" s="13"/>
@@ -6205,102 +6205,102 @@
         <v>42</v>
       </c>
       <c r="C43" s="11">
-        <f t="shared" ref="C43:J43" si="73">+C22/C19</f>
+        <f t="shared" ref="C43:J43" si="74">+C22/C19</f>
         <v>0.47088068181818182</v>
       </c>
       <c r="D43" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.45944833264717994</v>
       </c>
       <c r="E43" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.45416554327311942</v>
       </c>
       <c r="F43" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.45751308248193373</v>
       </c>
       <c r="G43" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.44953890115599426</v>
       </c>
       <c r="H43" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.45757767913760306</v>
       </c>
       <c r="I43" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.46565566458519181</v>
       </c>
       <c r="J43" s="11">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.47035620368156827</v>
       </c>
       <c r="K43" s="11">
-        <f t="shared" ref="K43:L43" si="74">+K22/K19</f>
+        <f t="shared" ref="K43:L43" si="75">+K22/K19</f>
         <v>0.4769605955589783</v>
       </c>
       <c r="L43" s="11">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.46380308880308879</v>
       </c>
       <c r="M43" s="11">
-        <f t="shared" ref="M43:P43" si="75">+M22/M19</f>
+        <f t="shared" ref="M43:P43" si="76">+M22/M19</f>
         <v>0.45990257811571816</v>
       </c>
       <c r="N43" s="11">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0.46496081143384049</v>
       </c>
       <c r="O43" s="11">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0.45612354842571529</v>
       </c>
       <c r="P43" s="11" t="e">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
       <c r="S43" s="11"/>
       <c r="T43" s="11">
-        <f t="shared" ref="T43:W43" si="76">+T22/T19</f>
+        <f t="shared" ref="T43:W43" si="77">+T22/T19</f>
         <v>0.5242575170632725</v>
       </c>
       <c r="U43" s="11">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.52382770734687645</v>
       </c>
       <c r="V43" s="11">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.50611610898970938</v>
       </c>
       <c r="W43" s="11">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.54028809363042984</v>
       </c>
       <c r="X43" s="11">
-        <f t="shared" ref="X43:AC43" si="77">+X22/X19</f>
+        <f t="shared" ref="X43:AC43" si="78">+X22/X19</f>
         <v>0.54903514496131256</v>
       </c>
       <c r="Y43" s="11">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.55165346261479642</v>
       </c>
       <c r="Z43" s="11">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.50050875790391747</v>
       </c>
       <c r="AA43" s="11">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.46031372812468507</v>
       </c>
       <c r="AB43" s="11">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.46098688555524103</v>
       </c>
       <c r="AC43" s="11">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.46620643916556131</v>
       </c>
       <c r="AD43" s="11"/>
@@ -6328,102 +6328,102 @@
         <v>43</v>
       </c>
       <c r="C44" s="11">
-        <f t="shared" ref="C44:J44" si="78">+C28/C19</f>
+        <f t="shared" ref="C44:J44" si="79">+C28/C19</f>
         <v>0.14190340909090909</v>
       </c>
       <c r="D44" s="11">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.15548236585700562</v>
       </c>
       <c r="E44" s="11">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.15745483957940146</v>
       </c>
       <c r="F44" s="11">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.21530027410914529</v>
       </c>
       <c r="G44" s="11">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.15170801402779582</v>
       </c>
       <c r="H44" s="11">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.16804058338617628</v>
       </c>
       <c r="I44" s="11">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.17726519689053141</v>
       </c>
       <c r="J44" s="11">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.17224480038250059</v>
       </c>
       <c r="K44" s="11">
-        <f t="shared" ref="K44:L44" si="79">+K28/K19</f>
+        <f t="shared" ref="K44:L44" si="80">+K28/K19</f>
         <v>0.19638043896804006</v>
       </c>
       <c r="L44" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.18146718146718147</v>
       </c>
       <c r="M44" s="11">
-        <f t="shared" ref="M44:P44" si="80">+M28/M19</f>
+        <f t="shared" ref="M44:P44" si="81">+M28/M19</f>
         <v>0.18058690744920994</v>
       </c>
       <c r="N44" s="11">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.17415859843245735</v>
       </c>
       <c r="O44" s="11">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.17813959056626361</v>
       </c>
       <c r="P44" s="11" t="e">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
       <c r="S44" s="11"/>
       <c r="T44" s="11">
-        <f t="shared" ref="T44:V44" si="81">+T28/T19</f>
+        <f t="shared" ref="T44:V44" si="82">+T28/T19</f>
         <v>0.14628297362110312</v>
       </c>
       <c r="U44" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.16244081258591722</v>
       </c>
       <c r="V44" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.1419972817293379</v>
       </c>
       <c r="W44" s="11">
-        <f t="shared" ref="W44:AB44" si="82">+W28/W19</f>
+        <f t="shared" ref="W44:AB44" si="83">+W28/W19</f>
         <v>0.15299347287868556</v>
       </c>
       <c r="X44" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.15330474503589075</v>
       </c>
       <c r="Y44" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.16798707185369122</v>
       </c>
       <c r="Z44" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.13943600552365723</v>
       </c>
       <c r="AA44" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.16888918746431092</v>
       </c>
       <c r="AB44" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.16746862911595434</v>
       </c>
       <c r="AC44" s="11">
-        <f t="shared" ref="AC44" si="83">+AC28/AC19</f>
+        <f t="shared" ref="AC44" si="84">+AC28/AC19</f>
         <v>0.1828349210177258</v>
       </c>
       <c r="AD44" s="11"/>
@@ -6451,27 +6451,27 @@
         <v>44</v>
       </c>
       <c r="C45" s="11">
-        <f t="shared" ref="C45:H45" si="84">+C31/C30</f>
+        <f t="shared" ref="C45:H45" si="85">+C31/C30</f>
         <v>0.25977653631284914</v>
       </c>
       <c r="D45" s="11">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.21028396009209516</v>
       </c>
       <c r="E45" s="11">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.17808219178082191</v>
       </c>
       <c r="F45" s="11">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.2180702732849972</v>
       </c>
       <c r="G45" s="11">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.26550868486352358</v>
       </c>
       <c r="H45" s="11">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.1937097927090779</v>
       </c>
       <c r="I45" s="11">
@@ -6479,15 +6479,15 @@
         <v>0.2295957284515637</v>
       </c>
       <c r="J45" s="11">
-        <f t="shared" ref="J45:AB45" si="85">+J31/J30</f>
+        <f t="shared" ref="J45:AB45" si="86">+J31/J30</f>
         <v>0.20496453900709219</v>
       </c>
       <c r="K45" s="11">
-        <f t="shared" ref="K45:L45" si="86">+K31/K30</f>
+        <f t="shared" ref="K45:L45" si="87">+K31/K30</f>
         <v>0.19713038053649407</v>
       </c>
       <c r="L45" s="11">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.17593198168737736</v>
       </c>
       <c r="M45" s="11">
@@ -6495,58 +6495,58 @@
         <v>0.18590998043052837</v>
       </c>
       <c r="N45" s="11">
-        <f t="shared" ref="N45:P45" si="87">+N31/N30</f>
+        <f t="shared" ref="N45:P45" si="88">+N31/N30</f>
         <v>0.11677934849416104</v>
       </c>
       <c r="O45" s="11">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.20100502512562815</v>
       </c>
       <c r="P45" s="11" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q45" s="11"/>
       <c r="R45" s="11"/>
       <c r="S45" s="11"/>
       <c r="T45" s="11">
-        <f t="shared" ref="T45:V45" si="88">+T31/T30</f>
+        <f t="shared" ref="T45:V45" si="89">+T31/T30</f>
         <v>0.14101778050275904</v>
       </c>
       <c r="U45" s="11">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.18409090909090908</v>
       </c>
       <c r="V45" s="11">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.13425925925925927</v>
       </c>
       <c r="W45" s="11">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.17978652434956638</v>
       </c>
       <c r="X45" s="11">
-        <f t="shared" ref="X45:Y45" si="89">+X31/X30</f>
+        <f t="shared" ref="X45:Y45" si="90">+X31/X30</f>
         <v>0.17038499506416585</v>
       </c>
       <c r="Y45" s="11">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-1.7077335935594046E-2</v>
       </c>
       <c r="Z45" s="11">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.28134284016636957</v>
       </c>
       <c r="AA45" s="11">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.21530216226205878</v>
       </c>
       <c r="AB45" s="11">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.22180521673860012</v>
       </c>
       <c r="AC45" s="11">
-        <f t="shared" ref="AC45" si="90">+AC31/AC30</f>
+        <f t="shared" ref="AC45" si="91">+AC31/AC30</f>
         <v>0.16830896376350921</v>
       </c>
       <c r="AD45" s="11"/>
@@ -6959,31 +6959,31 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="U54" s="17">
-        <f t="shared" ref="U54:AA54" si="91">+SUM(U48:U53)</f>
+        <f t="shared" ref="U54:AA54" si="92">+SUM(U48:U53)</f>
         <v>32645</v>
       </c>
       <c r="V54" s="17">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>32963</v>
       </c>
       <c r="W54" s="17">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>38495</v>
       </c>
       <c r="X54" s="17">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>50995</v>
       </c>
       <c r="Y54" s="17">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>52574</v>
       </c>
       <c r="Z54" s="17">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>57517</v>
       </c>
       <c r="AA54" s="17">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>62569</v>
       </c>
       <c r="AB54" s="17">
@@ -7270,23 +7270,23 @@
         <v>10369</v>
       </c>
       <c r="W60" s="17">
-        <f t="shared" ref="W60:AA60" si="92">+SUM(W55:W59)</f>
+        <f t="shared" ref="W60:AA60" si="93">+SUM(W55:W59)</f>
         <v>12838</v>
       </c>
       <c r="X60" s="17">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>19384</v>
       </c>
       <c r="Y60" s="17">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>23229</v>
       </c>
       <c r="Z60" s="17">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>21200</v>
       </c>
       <c r="AA60" s="17">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>19597</v>
       </c>
       <c r="AB60" s="17">
@@ -7329,23 +7329,23 @@
         <v>43332</v>
       </c>
       <c r="W61" s="77">
-        <f t="shared" ref="W61:AA61" si="93">+W60+W54</f>
+        <f t="shared" ref="W61:AA61" si="94">+W60+W54</f>
         <v>51333</v>
       </c>
       <c r="X61" s="77">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>70379</v>
       </c>
       <c r="Y61" s="77">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>75803</v>
       </c>
       <c r="Z61" s="77">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>78717</v>
       </c>
       <c r="AA61" s="77">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>82166</v>
       </c>
       <c r="AB61" s="77">
@@ -7585,35 +7585,35 @@
         <v>22863</v>
       </c>
       <c r="V66" s="17">
-        <f t="shared" ref="V66:AC66" si="94">+SUM(V62:V65)</f>
+        <f t="shared" ref="V66:AC66" si="95">+SUM(V62:V65)</f>
         <v>25904</v>
       </c>
       <c r="W66" s="17">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>26919</v>
       </c>
       <c r="X66" s="17">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>38447</v>
       </c>
       <c r="Y66" s="17">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>43029</v>
       </c>
       <c r="Z66" s="17">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>45101</v>
       </c>
       <c r="AA66" s="17">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>48466</v>
       </c>
       <c r="AB66" s="17">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>48376</v>
       </c>
       <c r="AC66" s="17">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>46443</v>
       </c>
     </row>
@@ -7737,27 +7737,27 @@
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
       <c r="U69" s="17">
-        <f t="shared" ref="U69:Z69" si="95">+SUM(U67:U68)</f>
+        <f t="shared" ref="U69:Z69" si="96">+SUM(U67:U68)</f>
         <v>1917</v>
       </c>
       <c r="V69" s="17">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>2042</v>
       </c>
       <c r="W69" s="17">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>7485</v>
       </c>
       <c r="X69" s="17">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>11869</v>
       </c>
       <c r="Y69" s="17">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>11047</v>
       </c>
       <c r="Z69" s="17">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>13342</v>
       </c>
       <c r="AA69" s="17">
@@ -7796,31 +7796,31 @@
       <c r="S70" s="9"/>
       <c r="T70" s="77"/>
       <c r="U70" s="77">
-        <f t="shared" ref="U70:AA70" si="96">+U69+U66</f>
+        <f t="shared" ref="U70:AA70" si="97">+U69+U66</f>
         <v>24780</v>
       </c>
       <c r="V70" s="77">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>27946</v>
       </c>
       <c r="W70" s="77">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>34404</v>
       </c>
       <c r="X70" s="77">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>50316</v>
       </c>
       <c r="Y70" s="77">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>54076</v>
       </c>
       <c r="Z70" s="77">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>58443</v>
       </c>
       <c r="AA70" s="77">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>61115</v>
       </c>
       <c r="AB70" s="77">
@@ -7904,31 +7904,31 @@
       <c r="S72" s="9"/>
       <c r="T72" s="77"/>
       <c r="U72" s="77">
-        <f t="shared" ref="U72:AA72" si="97">+U70+U71</f>
+        <f t="shared" ref="U72:AA72" si="98">+U70+U71</f>
         <v>40774</v>
       </c>
       <c r="V72" s="77">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>43332</v>
       </c>
       <c r="W72" s="77">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>51333</v>
       </c>
       <c r="X72" s="77">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>70379</v>
       </c>
       <c r="Y72" s="77">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>75803</v>
       </c>
       <c r="Z72" s="77">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>78717</v>
       </c>
       <c r="AA72" s="77">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>82166</v>
       </c>
       <c r="AB72" s="77">
@@ -7981,35 +7981,35 @@
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
       <c r="T74" s="17">
-        <f t="shared" ref="T74:AA74" si="98">+T32</f>
+        <f t="shared" ref="T74:AA74" si="99">+T32</f>
         <v>1401</v>
       </c>
       <c r="U74" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1795</v>
       </c>
       <c r="V74" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>2057</v>
       </c>
       <c r="W74" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>2459</v>
       </c>
       <c r="X74" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>4202</v>
       </c>
       <c r="Y74" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>4169</v>
       </c>
       <c r="Z74" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>2419</v>
       </c>
       <c r="AA74" s="17">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>4246</v>
       </c>
       <c r="AB74" s="17">
@@ -8834,35 +8834,35 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="17">
-        <f t="shared" ref="T90:W90" si="99">+SUM(T85:T89)</f>
+        <f t="shared" ref="T90:W90" si="100">+SUM(T85:T89)</f>
         <v>-481</v>
       </c>
       <c r="U90" s="17">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>-581</v>
       </c>
       <c r="V90" s="17">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>622</v>
       </c>
       <c r="W90" s="17">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>-1075</v>
       </c>
       <c r="X90" s="17">
-        <f t="shared" ref="X90" si="100">+SUM(X85:X89)</f>
+        <f t="shared" ref="X90" si="101">+SUM(X85:X89)</f>
         <v>-952</v>
       </c>
       <c r="Y90" s="17">
-        <f t="shared" ref="Y90:AA90" si="101">+SUM(Y85:Y89)</f>
+        <f t="shared" ref="Y90:AA90" si="102">+SUM(Y85:Y89)</f>
         <v>-1102</v>
       </c>
       <c r="Z90" s="17">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>-454</v>
       </c>
       <c r="AA90" s="17">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>-1314</v>
       </c>
       <c r="AB90" s="17">
@@ -8896,35 +8896,35 @@
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
       <c r="T91" s="77">
-        <f t="shared" ref="T91:AA91" si="102">+SUM(T74:T84)+T90</f>
+        <f t="shared" ref="T91:AA91" si="103">+SUM(T74:T84)+T90</f>
         <v>3158</v>
       </c>
       <c r="U91" s="77">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>2531</v>
       </c>
       <c r="V91" s="77">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>5483</v>
       </c>
       <c r="W91" s="77">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>4071</v>
       </c>
       <c r="X91" s="77">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>5854</v>
       </c>
       <c r="Y91" s="77">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>6340</v>
       </c>
       <c r="Z91" s="77">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>5813</v>
       </c>
       <c r="AA91" s="77">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>4843</v>
       </c>
       <c r="AB91" s="77">
@@ -9480,35 +9480,35 @@
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
       <c r="T102" s="77">
-        <f t="shared" ref="T102:AA102" si="103">+SUM(T92:T101)</f>
+        <f t="shared" ref="T102:AA102" si="104">+SUM(T92:T101)</f>
         <v>-5904</v>
       </c>
       <c r="U102" s="77">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>-4485</v>
       </c>
       <c r="V102" s="77">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>840</v>
       </c>
       <c r="W102" s="77">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>-5742</v>
       </c>
       <c r="X102" s="77">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>-16218</v>
       </c>
       <c r="Y102" s="77">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>-5485</v>
       </c>
       <c r="Z102" s="77">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>-3328</v>
       </c>
       <c r="AA102" s="77">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>752</v>
       </c>
       <c r="AB102" s="77">
@@ -9962,35 +9962,35 @@
       <c r="R111" s="3"/>
       <c r="S111" s="9"/>
       <c r="T111" s="77">
-        <f t="shared" ref="T111:AA111" si="104">+SUM(T103:T110)</f>
+        <f t="shared" ref="T111:AA111" si="105">+SUM(T103:T110)</f>
         <v>2038</v>
       </c>
       <c r="U111" s="77">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>4084</v>
       </c>
       <c r="V111" s="77">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>-1262</v>
       </c>
       <c r="W111" s="77">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>4187</v>
       </c>
       <c r="X111" s="77">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>12492</v>
       </c>
       <c r="Y111" s="77">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>-764</v>
       </c>
       <c r="Z111" s="77">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>-1203</v>
       </c>
       <c r="AA111" s="77">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>-2993</v>
       </c>
       <c r="AB111" s="77">
@@ -10076,43 +10076,43 @@
       <c r="R113" s="3"/>
       <c r="S113" s="3"/>
       <c r="T113" s="77">
-        <f t="shared" ref="T113" si="105">+SUM(T112,T111,T102,T91)</f>
+        <f t="shared" ref="T113" si="106">+SUM(T112,T111,T102,T91)</f>
         <v>-708</v>
       </c>
       <c r="U113" s="77">
-        <f t="shared" ref="U113" si="106">+SUM(U112,U111,U102,U91)</f>
+        <f t="shared" ref="U113" si="107">+SUM(U112,U111,U102,U91)</f>
         <v>2166</v>
       </c>
       <c r="V113" s="77">
-        <f t="shared" ref="V113" si="107">+SUM(V112,V111,V102,V91)</f>
+        <f t="shared" ref="V113" si="108">+SUM(V112,V111,V102,V91)</f>
         <v>4948</v>
       </c>
       <c r="W113" s="77">
-        <f t="shared" ref="W113:AC113" si="108">+SUM(W112,W111,W102,W91)</f>
+        <f t="shared" ref="W113:AC113" si="109">+SUM(W112,W111,W102,W91)</f>
         <v>2510</v>
       </c>
       <c r="X113" s="77">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>2297</v>
       </c>
       <c r="Y113" s="77">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>-11</v>
       </c>
       <c r="Z113" s="77">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>1127</v>
       </c>
       <c r="AA113" s="77">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>2678</v>
       </c>
       <c r="AB113" s="77">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>556</v>
       </c>
       <c r="AC113" s="77">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>1528</v>
       </c>
     </row>
@@ -10138,35 +10138,35 @@
       <c r="R114" s="3"/>
       <c r="S114" s="3"/>
       <c r="T114" s="17">
-        <f t="shared" ref="T114:AA114" si="109">+T115-T113</f>
+        <f t="shared" ref="T114:AA114" si="110">+T115-T113</f>
         <v>6827</v>
       </c>
       <c r="U114" s="17">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>6119</v>
       </c>
       <c r="V114" s="17">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>8285</v>
       </c>
       <c r="W114" s="17">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>13233</v>
       </c>
       <c r="X114" s="17">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>15743</v>
       </c>
       <c r="Y114" s="17">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>18040</v>
       </c>
       <c r="Z114" s="17">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>18029</v>
       </c>
       <c r="AA114" s="17">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>19156</v>
       </c>
       <c r="AB114" s="17">
@@ -10198,35 +10198,35 @@
       <c r="R115" s="3"/>
       <c r="S115" s="3"/>
       <c r="T115" s="17">
-        <f t="shared" ref="T115:AA115" si="110">+U114</f>
+        <f t="shared" ref="T115:AA115" si="111">+U114</f>
         <v>6119</v>
       </c>
       <c r="U115" s="17">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>8285</v>
       </c>
       <c r="V115" s="17">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>13233</v>
       </c>
       <c r="W115" s="17">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>15743</v>
       </c>
       <c r="X115" s="17">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>18040</v>
       </c>
       <c r="Y115" s="17">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>18029</v>
       </c>
       <c r="Z115" s="17">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>19156</v>
       </c>
       <c r="AA115" s="17">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>21834</v>
       </c>
       <c r="AB115" s="17">
@@ -13507,14 +13507,14 @@
       </c>
       <c r="J3" s="33">
         <f>+Main!I2</f>
-        <v>45.76</v>
+        <v>55.35</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>143</v>
       </c>
       <c r="O3" s="33">
         <f>+J3</f>
-        <v>45.76</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -13523,14 +13523,14 @@
       </c>
       <c r="E4" s="34">
         <f ca="1">+TODAY()</f>
-        <v>46150</v>
+        <v>46226</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>145</v>
       </c>
       <c r="J4" s="35">
         <f ca="1">V62</f>
-        <v>94.369818167718876</v>
+        <v>93.627712741650726</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>146</v>
@@ -13552,7 +13552,7 @@
       </c>
       <c r="J5" s="37">
         <f ca="1">J4/J3-1</f>
-        <v>1.0622774949239266</v>
+        <v>0.69155759244174742</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>148</v>
@@ -15136,43 +15136,43 @@
       <c r="L52" s="61"/>
       <c r="M52" s="61">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>1438.3370394135227</v>
+        <v>2240.5237173286137</v>
       </c>
       <c r="N52" s="61">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>4172.1549702670309</v>
+        <v>4097.9178163895058</v>
       </c>
       <c r="O52" s="61">
         <f t="shared" ref="O52:U52" ca="1" si="21">O51/(1+$E$18)^O53</f>
-        <v>4288.6968436877323</v>
+        <v>4212.3860043761906</v>
       </c>
       <c r="P52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>4394.5713962686505</v>
+        <v>4316.3766802776272</v>
       </c>
       <c r="Q52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>4335.7981738200697</v>
+        <v>4258.6492379570354</v>
       </c>
       <c r="R52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>4193.2525065344207</v>
+        <v>4118.6399540781076</v>
       </c>
       <c r="S52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>4044.9746059056602</v>
+        <v>3973.000433232472</v>
       </c>
       <c r="T52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>3892.392265999616</v>
+        <v>3823.1330640615324</v>
       </c>
       <c r="U52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>3736.8373806509303</v>
+        <v>3670.3460413743078</v>
       </c>
       <c r="V52" s="62">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>3579.538669163649</v>
+        <v>3515.8462212831128</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.2">
@@ -15181,43 +15181,43 @@
       </c>
       <c r="M53" s="23">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.35555555555555557</v>
+        <v>0.56388888888888888</v>
       </c>
       <c r="N53" s="23">
         <f ca="1">M53+1</f>
-        <v>1.3555555555555556</v>
+        <v>1.5638888888888889</v>
       </c>
       <c r="O53" s="23">
         <f ca="1">N53+1</f>
-        <v>2.3555555555555556</v>
+        <v>2.5638888888888891</v>
       </c>
       <c r="P53" s="23">
         <f t="shared" ref="P53:V53" ca="1" si="22">O53+1</f>
-        <v>3.3555555555555556</v>
+        <v>3.5638888888888891</v>
       </c>
       <c r="Q53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>4.3555555555555561</v>
+        <v>4.5638888888888891</v>
       </c>
       <c r="R53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>5.3555555555555561</v>
+        <v>5.5638888888888891</v>
       </c>
       <c r="S53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>6.3555555555555561</v>
+        <v>6.5638888888888891</v>
       </c>
       <c r="T53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>7.3555555555555561</v>
+        <v>7.5638888888888891</v>
       </c>
       <c r="U53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>8.3555555555555561</v>
+        <v>8.56388888888889</v>
       </c>
       <c r="V53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>9.3555555555555561</v>
+        <v>9.56388888888889</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -15230,7 +15230,7 @@
       <c r="Q54" s="24"/>
       <c r="V54" s="17">
         <f ca="1">SUM(M52:V52)</f>
-        <v>38076.553851711287</v>
+        <v>38226.819170358503</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.2">
@@ -15274,7 +15274,7 @@
       <c r="U56" s="63"/>
       <c r="V56" s="64">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>45234.581127444741</v>
+        <v>44429.700536077689</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.2">
@@ -15302,7 +15302,7 @@
       <c r="U57" s="65"/>
       <c r="V57" s="66">
         <f ca="1">V54+V56</f>
-        <v>83311.134979156021</v>
+        <v>82656.5197064362</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.2">
@@ -15356,7 +15356,7 @@
       <c r="Q60" s="24"/>
       <c r="V60" s="67">
         <f ca="1">V57+V58-V59</f>
-        <v>83244.134979156021</v>
+        <v>82589.5197064362</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.2">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="V62" s="67">
         <f ca="1">V60/V61</f>
-        <v>94.369818167718876</v>
+        <v>93.627712741650726</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.2">
@@ -15426,35 +15426,35 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B68" s="68"/>
-      <c r="C68" s="79" t="s">
+      <c r="C68" s="81" t="s">
         <v>162</v>
       </c>
-      <c r="D68" s="79"/>
-      <c r="E68" s="79"/>
-      <c r="F68" s="79"/>
-      <c r="G68" s="79"/>
-      <c r="H68" s="79"/>
-      <c r="I68" s="79"/>
-      <c r="J68" s="80"/>
+      <c r="D68" s="81"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="81"/>
+      <c r="H68" s="81"/>
+      <c r="I68" s="81"/>
+      <c r="J68" s="82"/>
       <c r="M68" s="68"/>
-      <c r="N68" s="81" t="s">
+      <c r="N68" s="83" t="s">
         <v>190</v>
       </c>
-      <c r="O68" s="81"/>
-      <c r="P68" s="81"/>
-      <c r="Q68" s="81"/>
-      <c r="R68" s="81"/>
-      <c r="S68" s="81"/>
-      <c r="T68" s="81"/>
-      <c r="U68" s="82"/>
+      <c r="O68" s="83"/>
+      <c r="P68" s="83"/>
+      <c r="Q68" s="83"/>
+      <c r="R68" s="83"/>
+      <c r="S68" s="83"/>
+      <c r="T68" s="83"/>
+      <c r="U68" s="84"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B69" s="83" t="s">
+      <c r="B69" s="85" t="s">
         <v>160</v>
       </c>
       <c r="C69" s="69">
         <f ca="1">+J4</f>
-        <v>94.369818167718876</v>
+        <v>93.627712741650726</v>
       </c>
       <c r="D69" s="70">
         <v>0.01</v>
@@ -15477,12 +15477,12 @@
       <c r="J69" s="70">
         <v>0.04</v>
       </c>
-      <c r="M69" s="83" t="s">
+      <c r="M69" s="85" t="s">
         <v>160</v>
       </c>
       <c r="N69" s="69">
         <f ca="1">+J4</f>
-        <v>94.369818167718876</v>
+        <v>93.627712741650726</v>
       </c>
       <c r="O69" s="70">
         <v>7.0000000000000007E-2</v>
@@ -15507,369 +15507,369 @@
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B70" s="83"/>
+      <c r="B70" s="85"/>
       <c r="C70" s="71">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D70" s="72">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>115.26398911187168</v>
+        <v>114.48498562482762</v>
       </c>
       <c r="E70" s="72">
-        <v>117.21151743275539</v>
+        <v>116.40339086406972</v>
       </c>
       <c r="F70" s="72">
-        <v>119.46826855032323</v>
+        <v>118.62639482307925</v>
       </c>
       <c r="G70" s="73">
-        <v>122.12700930358044</v>
+        <v>121.2453771177864</v>
       </c>
       <c r="H70" s="72">
-        <v>125.32173623775681</v>
+        <v>124.39233052675705</v>
       </c>
       <c r="I70" s="72">
-        <v>129.25344417069704</v>
+        <v>128.26524421784003</v>
       </c>
       <c r="J70" s="72">
-        <v>134.23798210187144</v>
-      </c>
-      <c r="M70" s="83"/>
+        <v>133.17524402622641</v>
+      </c>
+      <c r="M70" s="85"/>
       <c r="N70" s="71">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="O70" s="72">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>111.28530876362561</v>
+        <v>110.56580193774187</v>
       </c>
       <c r="P70" s="72">
-        <v>115.80268398860677</v>
+        <v>115.01562492942708</v>
       </c>
       <c r="Q70" s="72">
-        <v>119.31619805248104</v>
+        <v>118.47659836740448</v>
       </c>
       <c r="R70" s="73">
-        <v>122.12700930358044</v>
+        <v>121.2453771177864</v>
       </c>
       <c r="S70" s="72">
-        <v>124.42676396357085</v>
+        <v>123.51074154991706</v>
       </c>
       <c r="T70" s="72">
-        <v>126.34322618022955</v>
+        <v>125.39854524335927</v>
       </c>
       <c r="U70" s="72">
-        <v>127.96484805586378</v>
+        <v>126.99591759934883</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B71" s="83"/>
+      <c r="B71" s="85"/>
       <c r="C71" s="71">
         <v>0.08</v>
       </c>
       <c r="D71" s="72">
-        <v>106.52522917054493</v>
+        <v>105.77296631523038</v>
       </c>
       <c r="E71" s="72">
-        <v>107.88340643040195</v>
+        <v>107.1095408189903</v>
       </c>
       <c r="F71" s="72">
-        <v>109.42856029199842</v>
+        <v>108.63011793129846</v>
       </c>
       <c r="G71" s="73">
-        <v>111.21168437399044</v>
+        <v>110.38488018175886</v>
       </c>
       <c r="H71" s="72">
-        <v>113.30416974249675</v>
+        <v>112.44408311181721</v>
       </c>
       <c r="I71" s="72">
-        <v>115.80913682635543</v>
+        <v>114.90920694800614</v>
       </c>
       <c r="J71" s="72">
-        <v>118.88126626882368</v>
-      </c>
-      <c r="M71" s="83"/>
+        <v>117.93247203012473</v>
+      </c>
+      <c r="M71" s="85"/>
       <c r="N71" s="71">
         <v>0.08</v>
       </c>
       <c r="O71" s="72">
-        <v>101.77432369907561</v>
+        <v>101.09762730711897</v>
       </c>
       <c r="P71" s="72">
-        <v>105.70655731362346</v>
+        <v>104.9673160048856</v>
       </c>
       <c r="Q71" s="72">
-        <v>108.76496123604956</v>
+        <v>107.97707388092628</v>
       </c>
       <c r="R71" s="73">
-        <v>111.21168437399044</v>
+        <v>110.38488018175886</v>
       </c>
       <c r="S71" s="72">
-        <v>113.21354875957842</v>
+        <v>112.35490351880367</v>
       </c>
       <c r="T71" s="72">
-        <v>114.88176908090175</v>
+        <v>113.99658963300769</v>
       </c>
       <c r="U71" s="72">
-        <v>116.29334012202149</v>
+        <v>115.38570865271878</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B72" s="83"/>
+      <c r="B72" s="85"/>
       <c r="C72" s="71">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="D72" s="73">
-        <v>98.962905150828703</v>
+        <v>98.234730447108362</v>
       </c>
       <c r="E72" s="73">
-        <v>99.89083027213394</v>
+        <v>99.147017973595979</v>
       </c>
       <c r="F72" s="73">
-        <v>100.92669415051405</v>
+        <v>100.16542524988142</v>
       </c>
       <c r="G72" s="73">
-        <v>102.09748147523777</v>
+        <v>101.3164822134141</v>
       </c>
       <c r="H72" s="73">
-        <v>103.43998954985339</v>
+        <v>102.63636605162513</v>
       </c>
       <c r="I72" s="73">
-        <v>105.00573459932849</v>
+        <v>104.17572482691799</v>
       </c>
       <c r="J72" s="73">
-        <v>106.86912894861622</v>
-      </c>
-      <c r="M72" s="83"/>
+        <v>106.00771685165329</v>
+      </c>
+      <c r="M72" s="85"/>
       <c r="N72" s="71">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="O72" s="73">
-        <v>93.812435749298388</v>
+        <v>93.171057869774643</v>
       </c>
       <c r="P72" s="73">
-        <v>97.264538135106477</v>
+        <v>96.56498467962443</v>
       </c>
       <c r="Q72" s="73">
-        <v>99.949506657401642</v>
+        <v>99.2047055317298</v>
       </c>
       <c r="R72" s="73">
-        <v>102.09748147523777</v>
+        <v>101.3164822134141</v>
       </c>
       <c r="S72" s="73">
-        <v>103.85491541710373</v>
+        <v>103.04429949842853</v>
       </c>
       <c r="T72" s="73">
-        <v>105.31944370199199</v>
+        <v>104.48414723594057</v>
       </c>
       <c r="U72" s="73">
-        <v>106.55865994305131</v>
+        <v>105.7024799369123</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B73" s="83"/>
+      <c r="B73" s="85"/>
       <c r="C73" s="71">
         <v>0.09</v>
       </c>
       <c r="D73" s="72">
-        <v>92.356130706074083</v>
+        <v>91.649855786546738</v>
       </c>
       <c r="E73" s="72">
-        <v>92.966768574015234</v>
+        <v>92.249628282111033</v>
       </c>
       <c r="F73" s="72">
-        <v>93.633669778901094</v>
+        <v>92.904662994088312</v>
       </c>
       <c r="G73" s="73">
-        <v>94.369818167718876</v>
+        <v>93.627712741650726</v>
       </c>
       <c r="H73" s="72">
-        <v>95.192525536451612</v>
+        <v>94.435781283694595</v>
       </c>
       <c r="I73" s="72">
-        <v>96.125398879621514</v>
+        <v>95.352055564169405</v>
       </c>
       <c r="J73" s="72">
-        <v>97.201487989559766</v>
-      </c>
-      <c r="M73" s="83"/>
+        <v>96.408997304604426</v>
+      </c>
+      <c r="M73" s="85"/>
       <c r="N73" s="71">
         <v>0.09</v>
       </c>
       <c r="O73" s="72">
-        <v>87.044069638221416</v>
+        <v>86.432314768335374</v>
       </c>
       <c r="P73" s="72">
-        <v>90.096464858845366</v>
+        <v>89.430397257216768</v>
       </c>
       <c r="Q73" s="72">
-        <v>92.470550030441757</v>
+        <v>91.762239193013414</v>
       </c>
       <c r="R73" s="73">
-        <v>94.369818167718876</v>
+        <v>93.627712741650726</v>
       </c>
       <c r="S73" s="72">
-        <v>95.923764825491077</v>
+        <v>95.154009281444885</v>
       </c>
       <c r="T73" s="72">
-        <v>97.218720373634582</v>
+        <v>96.425923064606678</v>
       </c>
       <c r="U73" s="72">
-        <v>98.314451991294447</v>
+        <v>97.502157804205126</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B74" s="83"/>
+      <c r="B74" s="85"/>
       <c r="C74" s="71">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="D74" s="72">
-        <v>86.536002158007065</v>
+        <v>85.849794883844709</v>
       </c>
       <c r="E74" s="72">
-        <v>86.910945430858789</v>
+        <v>86.217715641718826</v>
       </c>
       <c r="F74" s="72">
-        <v>87.308186755782373</v>
+        <v>86.607516819409554</v>
       </c>
       <c r="G74" s="73">
-        <v>87.732504286793159</v>
+        <v>87.023887078306032</v>
       </c>
       <c r="H74" s="72">
-        <v>88.190146379142078</v>
+        <v>87.472957744840443</v>
       </c>
       <c r="I74" s="72">
-        <v>88.689444173163665</v>
+        <v>87.962903920922258</v>
       </c>
       <c r="J74" s="72">
-        <v>89.241758314768646</v>
-      </c>
-      <c r="M74" s="83"/>
+        <v>88.504873472791687</v>
+      </c>
+      <c r="M74" s="85"/>
       <c r="N74" s="71">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="O74" s="72">
-        <v>81.215139612176742</v>
+        <v>80.628589645205423</v>
       </c>
       <c r="P74" s="72">
-        <v>83.930708226600245</v>
+        <v>83.293296908997334</v>
       </c>
       <c r="Q74" s="72">
-        <v>86.042817148929643</v>
+        <v>85.365847003057723</v>
       </c>
       <c r="R74" s="73">
-        <v>87.732504286793159</v>
+        <v>87.023887078306032</v>
       </c>
       <c r="S74" s="72">
-        <v>89.114975581408757</v>
+        <v>88.380465321691005</v>
       </c>
       <c r="T74" s="72">
-        <v>90.267034993588453</v>
+        <v>89.510947191178488</v>
       </c>
       <c r="U74" s="72">
-        <v>91.241854496202009</v>
+        <v>90.467508773052501</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="83"/>
+      <c r="B75" s="85"/>
       <c r="C75" s="71">
         <v>0.1</v>
       </c>
       <c r="D75" s="72">
-        <v>81.371158561149542</v>
+        <v>80.703465049646198</v>
       </c>
       <c r="E75" s="72">
-        <v>81.570199491938553</v>
+        <v>80.898592746221439</v>
       </c>
       <c r="F75" s="72">
-        <v>81.769240422727549</v>
+        <v>81.09372044279668</v>
       </c>
       <c r="G75" s="73">
-        <v>81.968281353516531</v>
+        <v>81.288848139371936</v>
       </c>
       <c r="H75" s="72">
-        <v>82.167322284305527</v>
+        <v>81.483975835947177</v>
       </c>
       <c r="I75" s="72">
-        <v>82.366363215094509</v>
+        <v>81.679103532522419</v>
       </c>
       <c r="J75" s="72">
-        <v>82.565404145883534</v>
-      </c>
-      <c r="M75" s="83"/>
+        <v>81.874231229097674</v>
+      </c>
+      <c r="M75" s="85"/>
       <c r="N75" s="71">
         <v>0.1</v>
       </c>
       <c r="O75" s="72">
-        <v>76.139225523267399</v>
+        <v>75.574394168239763</v>
       </c>
       <c r="P75" s="72">
-        <v>78.567998785871211</v>
+        <v>77.955416656211511</v>
       </c>
       <c r="Q75" s="72">
-        <v>80.457044656785271</v>
+        <v>79.807323035745085</v>
       </c>
       <c r="R75" s="73">
-        <v>81.968281353516531</v>
+        <v>81.288848139371936</v>
       </c>
       <c r="S75" s="72">
-        <v>83.204747741751191</v>
+        <v>82.501005042339358</v>
       </c>
       <c r="T75" s="72">
-        <v>84.23513639861342</v>
+        <v>83.511135794812219</v>
       </c>
       <c r="U75" s="72">
-        <v>85.107003723650692</v>
+        <v>84.365861816135393</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B76" s="84"/>
+      <c r="B76" s="86"/>
       <c r="C76" s="71">
         <v>0.105</v>
       </c>
       <c r="D76" s="72">
-        <v>76.757901756163619</v>
+        <v>76.107388876657666</v>
       </c>
       <c r="E76" s="72">
-        <v>76.825397287844211</v>
+        <v>76.17349492773215</v>
       </c>
       <c r="F76" s="72">
-        <v>76.878389647428165</v>
+        <v>76.225396372790613</v>
       </c>
       <c r="G76" s="73">
-        <v>76.914159490147313</v>
+        <v>76.260429848205078</v>
       </c>
       <c r="H76" s="72">
-        <v>76.929262312628737</v>
+        <v>76.275221760046733</v>
       </c>
       <c r="I76" s="72">
-        <v>76.919269467678618</v>
+        <v>76.265434630407128</v>
       </c>
       <c r="J76" s="72">
-        <v>76.878389647428165</v>
-      </c>
-      <c r="M76" s="84"/>
+        <v>76.225396372790613</v>
+      </c>
+      <c r="M76" s="86"/>
       <c r="N76" s="71">
         <v>0.105</v>
       </c>
       <c r="O76" s="72">
-        <v>71.676432520556475</v>
+        <v>71.130528091087228</v>
       </c>
       <c r="P76" s="72">
-        <v>73.858818757885984</v>
+        <v>73.267987156552977</v>
       </c>
       <c r="Q76" s="72">
-        <v>75.556230275808957</v>
+        <v>74.930455318581934</v>
       </c>
       <c r="R76" s="73">
-        <v>76.914159490147313</v>
+        <v>76.260429848205078</v>
       </c>
       <c r="S76" s="72">
-        <v>78.025192483696898</v>
+        <v>77.348590826987646</v>
       </c>
       <c r="T76" s="72">
-        <v>78.95105331165486</v>
+        <v>78.255391642639793</v>
       </c>
       <c r="U76" s="72">
-        <v>79.734474012234699</v>
+        <v>79.022684640499321</v>
       </c>
     </row>
   </sheetData>

--- a/PYPL.xlsx
+++ b/PYPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC06EC8-AC44-4368-84BD-1D9AECC834EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{450CF116-8EB8-4934-B670-153E652B4C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B690896D-DF4D-4BA1-A25A-CD8C19559281}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{B690896D-DF4D-4BA1-A25A-CD8C19559281}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1118,13 +1118,19 @@
     <numFmt numFmtId="169" formatCode="0.0"/>
     <numFmt numFmtId="170" formatCode="\F\Y#,##0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1450,150 +1456,153 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="9" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="18" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1654,15 +1663,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1677,7 +1686,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="10915650" y="885825"/>
+          <a:off x="11506200" y="990600"/>
           <a:ext cx="19050" cy="4695825"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -2096,7 +2105,7 @@
         <v>3</v>
       </c>
       <c r="I2" s="2">
-        <v>55.35</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -2104,10 +2113,10 @@
         <v>4</v>
       </c>
       <c r="I3" s="3">
-        <v>882.10549300000002</v>
-      </c>
-      <c r="J3" s="79" t="s">
-        <v>342</v>
+        <v>887</v>
+      </c>
+      <c r="J3" s="87" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -2119,7 +2128,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I3*I2</f>
-        <v>48824.539037549999</v>
+        <v>52066.9</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -2130,11 +2139,11 @@
         <v>6</v>
       </c>
       <c r="I5" s="3">
-        <f>6977+2365</f>
-        <v>9342</v>
-      </c>
-      <c r="J5" s="79" t="s">
-        <v>342</v>
+        <f>8306+2950</f>
+        <v>11256</v>
+      </c>
+      <c r="J5" s="87" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -2142,10 +2151,11 @@
         <v>7</v>
       </c>
       <c r="I6" s="3">
-        <v>9409</v>
-      </c>
-      <c r="J6" s="79" t="s">
-        <v>342</v>
+        <f>10895+2505</f>
+        <v>13400</v>
+      </c>
+      <c r="J6" s="87" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -2157,7 +2167,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>48891.539037549999</v>
+        <v>54210.9</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -2704,7 +2714,9 @@
       <c r="O7" s="3">
         <v>439</v>
       </c>
-      <c r="P7" s="3"/>
+      <c r="P7" s="3">
+        <v>439</v>
+      </c>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
@@ -2793,7 +2805,9 @@
       <c r="O8" s="3">
         <v>6475</v>
       </c>
-      <c r="P8" s="3"/>
+      <c r="P8" s="3">
+        <v>6750</v>
+      </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
@@ -2872,7 +2886,7 @@
         <v>63.737143718896093</v>
       </c>
       <c r="J9" s="8">
-        <f t="shared" ref="J9:O9" si="2">+J12/J8</f>
+        <f t="shared" ref="J9:P9" si="2">+J12/J8</f>
         <v>66.148360779573949</v>
       </c>
       <c r="K9" s="8">
@@ -2894,7 +2908,10 @@
         <f t="shared" si="2"/>
         <v>71.653281853281854</v>
       </c>
-      <c r="P9" s="8"/>
+      <c r="P9" s="8">
+        <f t="shared" si="2"/>
+        <v>72.066370370370365</v>
+      </c>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
       <c r="S9" s="3"/>
@@ -2990,7 +3007,7 @@
         <v>956.89908256880733</v>
       </c>
       <c r="L10" s="3">
-        <f t="shared" ref="L10:O10" si="8">+L12/L7</f>
+        <f t="shared" ref="L10:P10" si="8">+L12/L7</f>
         <v>1012.6643835616438</v>
       </c>
       <c r="M10" s="3">
@@ -3005,7 +3022,10 @@
         <f t="shared" si="8"/>
         <v>1056.8451025056947</v>
       </c>
-      <c r="P10" s="3"/>
+      <c r="P10" s="3">
+        <f t="shared" si="8"/>
+        <v>1108.0820045558087</v>
+      </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
@@ -3101,7 +3121,7 @@
         <v>13.864678899082568</v>
       </c>
       <c r="L11" s="3">
-        <f t="shared" ref="L11:O11" si="14">+L8/L7</f>
+        <f t="shared" ref="L11:P11" si="14">+L8/L7</f>
         <v>14.214611872146119</v>
       </c>
       <c r="M11" s="3">
@@ -3116,7 +3136,10 @@
         <f t="shared" si="14"/>
         <v>14.749430523917995</v>
       </c>
-      <c r="P11" s="3"/>
+      <c r="P11" s="3">
+        <f>+P8/P7</f>
+        <v>15.375854214123008</v>
+      </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
@@ -3214,7 +3237,9 @@
       <c r="O12" s="9">
         <v>463955</v>
       </c>
-      <c r="P12" s="9"/>
+      <c r="P12" s="9">
+        <v>486448</v>
+      </c>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
@@ -3293,7 +3318,7 @@
         <v>1.8566584879365702E-2</v>
       </c>
       <c r="J13" s="10">
-        <f t="shared" ref="J13:O13" si="19">+J19/J12</f>
+        <f t="shared" ref="J13:P13" si="19">+J19/J12</f>
         <v>1.9107611068984735E-2</v>
       </c>
       <c r="K13" s="10">
@@ -3316,7 +3341,10 @@
         <f t="shared" si="19"/>
         <v>1.8003901240422025E-2</v>
       </c>
-      <c r="P13" s="10"/>
+      <c r="P13" s="10">
+        <f t="shared" si="19"/>
+        <v>1.7847745288293918E-2</v>
+      </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
       <c r="S13" s="11"/>
@@ -3455,7 +3483,9 @@
       <c r="O15" s="3">
         <v>4882</v>
       </c>
-      <c r="P15" s="3"/>
+      <c r="P15" s="3">
+        <v>5048</v>
+      </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
@@ -3545,7 +3575,9 @@
       <c r="O16" s="3">
         <v>3471</v>
       </c>
-      <c r="P16" s="3"/>
+      <c r="P16" s="3">
+        <v>3634</v>
+      </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
@@ -3641,7 +3673,9 @@
       <c r="O17" s="3">
         <v>7501</v>
       </c>
-      <c r="P17" s="3"/>
+      <c r="P17" s="3">
+        <v>7832</v>
+      </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
@@ -3731,7 +3765,9 @@
       <c r="O18" s="3">
         <v>852</v>
       </c>
-      <c r="P18" s="3"/>
+      <c r="P18" s="3">
+        <v>850</v>
+      </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
@@ -3829,7 +3865,9 @@
       <c r="O19" s="9">
         <v>8353</v>
       </c>
-      <c r="P19" s="9"/>
+      <c r="P19" s="9">
+        <v>8682</v>
+      </c>
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
@@ -3926,7 +3964,9 @@
       <c r="O20" s="3">
         <v>4165</v>
       </c>
-      <c r="P20" s="3"/>
+      <c r="P20" s="3">
+        <v>4385</v>
+      </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
@@ -4026,7 +4066,9 @@
       <c r="O21" s="3">
         <v>378</v>
       </c>
-      <c r="P21" s="3"/>
+      <c r="P21" s="3">
+        <v>397</v>
+      </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
@@ -4113,7 +4155,7 @@
         <v>3654</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" ref="J22:O22" si="30">+J19-SUM(J20:J21)</f>
+        <f t="shared" ref="J22:P22" si="30">+J19-SUM(J20:J21)</f>
         <v>3935</v>
       </c>
       <c r="K22" s="3">
@@ -4136,7 +4178,10 @@
         <f t="shared" si="30"/>
         <v>3810</v>
       </c>
-      <c r="P22" s="3"/>
+      <c r="P22" s="3">
+        <f t="shared" si="30"/>
+        <v>3900</v>
+      </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
@@ -4243,7 +4288,9 @@
       <c r="O23" s="3">
         <v>446</v>
       </c>
-      <c r="P23" s="3"/>
+      <c r="P23" s="3">
+        <v>462</v>
+      </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
@@ -4340,7 +4387,9 @@
       <c r="O24" s="3">
         <v>518</v>
       </c>
-      <c r="P24" s="3"/>
+      <c r="P24" s="3">
+        <v>546</v>
+      </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
@@ -4437,7 +4486,9 @@
       <c r="O25" s="3">
         <v>793</v>
       </c>
-      <c r="P25" s="3"/>
+      <c r="P25" s="3">
+        <v>849</v>
+      </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
@@ -4534,7 +4585,9 @@
       <c r="O26" s="3">
         <v>491</v>
       </c>
-      <c r="P26" s="3"/>
+      <c r="P26" s="3">
+        <v>503</v>
+      </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
@@ -4631,7 +4684,9 @@
       <c r="O27" s="3">
         <v>74</v>
       </c>
-      <c r="P27" s="3"/>
+      <c r="P27" s="3">
+        <v>113</v>
+      </c>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
@@ -4741,7 +4796,10 @@
         <f>+O22-SUM(O23:O27)</f>
         <v>1488</v>
       </c>
-      <c r="P28" s="3"/>
+      <c r="P28" s="3">
+        <f>+P22-SUM(P23:P27)</f>
+        <v>1427</v>
+      </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
@@ -4848,7 +4906,9 @@
       <c r="O29" s="3">
         <v>-95</v>
       </c>
-      <c r="P29" s="3"/>
+      <c r="P29" s="3">
+        <v>-117</v>
+      </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -4958,7 +5018,10 @@
         <f>+O28+O29</f>
         <v>1393</v>
       </c>
-      <c r="P30" s="3"/>
+      <c r="P30" s="3">
+        <f>+P28+P29</f>
+        <v>1310</v>
+      </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
@@ -5065,7 +5128,9 @@
       <c r="O31" s="3">
         <v>280</v>
       </c>
-      <c r="P31" s="3"/>
+      <c r="P31" s="3">
+        <v>206</v>
+      </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
@@ -5175,7 +5240,10 @@
         <f>+O30-O31</f>
         <v>1113</v>
       </c>
-      <c r="P32" s="3"/>
+      <c r="P32" s="3">
+        <f>+P30-P31</f>
+        <v>1104</v>
+      </c>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
@@ -5308,7 +5376,7 @@
         <v>1.3017641597028784</v>
       </c>
       <c r="G34" s="12">
-        <f t="shared" ref="G34:O34" si="49">+G32/G35</f>
+        <f t="shared" ref="G34:P34" si="49">+G32/G35</f>
         <v>0.83458646616541354</v>
       </c>
       <c r="H34" s="12">
@@ -5343,7 +5411,10 @@
         <f t="shared" si="49"/>
         <v>1.2190580503833517</v>
       </c>
-      <c r="P34" s="12"/>
+      <c r="P34" s="12">
+        <f t="shared" si="49"/>
+        <v>1.2446448703494928</v>
+      </c>
       <c r="Q34" s="12"/>
       <c r="R34" s="12"/>
       <c r="S34" s="12"/>
@@ -5450,7 +5521,9 @@
       <c r="O35" s="3">
         <v>913</v>
       </c>
-      <c r="P35" s="3"/>
+      <c r="P35" s="3">
+        <v>887</v>
+      </c>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
@@ -5598,7 +5671,7 @@
       </c>
       <c r="P37" s="11">
         <f t="shared" ref="P37:P38" si="55">+P7/L7-1</f>
-        <v>-1</v>
+        <v>2.2831050228311334E-3</v>
       </c>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
@@ -5706,7 +5779,7 @@
       </c>
       <c r="P38" s="11">
         <f t="shared" si="55"/>
-        <v>-1</v>
+        <v>8.4163186636684761E-2</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
@@ -5814,7 +5887,7 @@
       </c>
       <c r="P39" s="11">
         <f t="shared" ref="P39" si="63">+P12/L12-1</f>
-        <v>-1</v>
+        <v>9.6722557023269262E-2</v>
       </c>
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
@@ -5922,7 +5995,7 @@
       </c>
       <c r="P40" s="11">
         <f t="shared" ref="P40:P42" si="69">+P17/L17-1</f>
-        <v>-1</v>
+        <v>5.2546700712269967E-2</v>
       </c>
       <c r="Q40" s="11"/>
       <c r="R40" s="11"/>
@@ -6030,7 +6103,7 @@
       </c>
       <c r="P41" s="11">
         <f t="shared" si="69"/>
-        <v>-1</v>
+        <v>3.5419126328217754E-3</v>
       </c>
       <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
@@ -6138,7 +6211,7 @@
       </c>
       <c r="P42" s="13">
         <f t="shared" si="69"/>
-        <v>-1</v>
+        <v>4.753861003860993E-2</v>
       </c>
       <c r="Q42" s="13"/>
       <c r="R42" s="13"/>
@@ -6256,9 +6329,9 @@
         <f t="shared" si="76"/>
         <v>0.45612354842571529</v>
       </c>
-      <c r="P43" s="11" t="e">
+      <c r="P43" s="11">
         <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
+        <v>0.44920525224602625</v>
       </c>
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
@@ -6379,9 +6452,9 @@
         <f t="shared" si="81"/>
         <v>0.17813959056626361</v>
       </c>
-      <c r="P44" s="11" t="e">
+      <c r="P44" s="11">
         <f t="shared" si="81"/>
-        <v>#DIV/0!</v>
+        <v>0.16436304998848192</v>
       </c>
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
@@ -6502,9 +6575,9 @@
         <f t="shared" si="88"/>
         <v>0.20100502512562815</v>
       </c>
-      <c r="P45" s="11" t="e">
+      <c r="P45" s="11">
         <f t="shared" si="88"/>
-        <v>#DIV/0!</v>
+        <v>0.15725190839694655</v>
       </c>
       <c r="Q45" s="11"/>
       <c r="R45" s="11"/>
@@ -13507,14 +13580,14 @@
       </c>
       <c r="J3" s="33">
         <f>+Main!I2</f>
-        <v>55.35</v>
+        <v>58.7</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>143</v>
       </c>
       <c r="O3" s="33">
         <f>+J3</f>
-        <v>55.35</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -13523,14 +13596,14 @@
       </c>
       <c r="E4" s="34">
         <f ca="1">+TODAY()</f>
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>145</v>
       </c>
       <c r="J4" s="35">
         <f ca="1">V62</f>
-        <v>93.627712741650726</v>
+        <v>90.720141570568231</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>146</v>
@@ -13552,7 +13625,7 @@
       </c>
       <c r="J5" s="37">
         <f ca="1">J4/J3-1</f>
-        <v>0.69155759244174742</v>
+        <v>0.54548793135550633</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>148</v>
@@ -15136,43 +15209,43 @@
       <c r="L52" s="61"/>
       <c r="M52" s="61">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>2240.5237173286137</v>
+        <v>2292.9629116079386</v>
       </c>
       <c r="N52" s="61">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>4097.9178163895058</v>
+        <v>4093.015901711593</v>
       </c>
       <c r="O52" s="61">
         <f t="shared" ref="O52:U52" ca="1" si="21">O51/(1+$E$18)^O53</f>
-        <v>4212.3860043761906</v>
+        <v>4207.3471632600258</v>
       </c>
       <c r="P52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>4316.3766802776272</v>
+        <v>4311.2134458858036</v>
       </c>
       <c r="Q52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>4258.6492379570354</v>
+        <v>4253.5550569258476</v>
       </c>
       <c r="R52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>4118.6399540781076</v>
+        <v>4113.7132516529928</v>
       </c>
       <c r="S52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>3973.000433232472</v>
+        <v>3968.2479442828103</v>
       </c>
       <c r="T52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>3823.1330640615324</v>
+        <v>3818.5598459244143</v>
       </c>
       <c r="U52" s="61">
         <f t="shared" ca="1" si="21"/>
-        <v>3670.3460413743078</v>
+        <v>3665.9555865288567</v>
       </c>
       <c r="V52" s="62">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>3515.8462212831128</v>
+        <v>3511.6405785714746</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.2">
@@ -15181,43 +15254,43 @@
       </c>
       <c r="M53" s="23">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.56388888888888888</v>
+        <v>0.57777777777777772</v>
       </c>
       <c r="N53" s="23">
         <f ca="1">M53+1</f>
-        <v>1.5638888888888889</v>
+        <v>1.5777777777777777</v>
       </c>
       <c r="O53" s="23">
         <f ca="1">N53+1</f>
-        <v>2.5638888888888891</v>
+        <v>2.5777777777777775</v>
       </c>
       <c r="P53" s="23">
         <f t="shared" ref="P53:V53" ca="1" si="22">O53+1</f>
-        <v>3.5638888888888891</v>
+        <v>3.5777777777777775</v>
       </c>
       <c r="Q53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>4.5638888888888891</v>
+        <v>4.5777777777777775</v>
       </c>
       <c r="R53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>5.5638888888888891</v>
+        <v>5.5777777777777775</v>
       </c>
       <c r="S53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>6.5638888888888891</v>
+        <v>6.5777777777777775</v>
       </c>
       <c r="T53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>7.5638888888888891</v>
+        <v>7.5777777777777775</v>
       </c>
       <c r="U53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>8.56388888888889</v>
+        <v>8.5777777777777775</v>
       </c>
       <c r="V53" s="23">
         <f t="shared" ca="1" si="22"/>
-        <v>9.56388888888889</v>
+        <v>9.5777777777777775</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -15230,7 +15303,7 @@
       <c r="Q54" s="24"/>
       <c r="V54" s="17">
         <f ca="1">SUM(M52:V52)</f>
-        <v>38226.819170358503</v>
+        <v>38236.211686351759</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.2">
@@ -15274,7 +15347,7 @@
       <c r="U56" s="63"/>
       <c r="V56" s="64">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>44429.700536077689</v>
+        <v>44376.553886742266</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.2">
@@ -15302,7 +15375,7 @@
       <c r="U57" s="65"/>
       <c r="V57" s="66">
         <f ca="1">V54+V56</f>
-        <v>82656.5197064362</v>
+        <v>82612.765573094017</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.2">
@@ -15315,7 +15388,7 @@
       <c r="Q58" s="24"/>
       <c r="V58" s="67">
         <f>+Main!I5</f>
-        <v>9342</v>
+        <v>11256</v>
       </c>
     </row>
     <row r="59" spans="2:24" x14ac:dyDescent="0.2">
@@ -15343,7 +15416,7 @@
       <c r="U59" s="63"/>
       <c r="V59" s="64">
         <f>+Main!I6</f>
-        <v>9409</v>
+        <v>13400</v>
       </c>
     </row>
     <row r="60" spans="2:24" x14ac:dyDescent="0.2">
@@ -15356,7 +15429,7 @@
       <c r="Q60" s="24"/>
       <c r="V60" s="67">
         <f ca="1">V57+V58-V59</f>
-        <v>82589.5197064362</v>
+        <v>80468.765573094017</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.2">
@@ -15384,7 +15457,7 @@
       <c r="U61" s="63"/>
       <c r="V61" s="64">
         <f>+Main!I3</f>
-        <v>882.10549300000002</v>
+        <v>887</v>
       </c>
     </row>
     <row r="62" spans="2:24" x14ac:dyDescent="0.2">
@@ -15393,7 +15466,7 @@
       </c>
       <c r="V62" s="67">
         <f ca="1">V60/V61</f>
-        <v>93.627712741650726</v>
+        <v>90.720141570568231</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.2">
@@ -15454,7 +15527,7 @@
       </c>
       <c r="C69" s="69">
         <f ca="1">+J4</f>
-        <v>93.627712741650726</v>
+        <v>90.720141570568231</v>
       </c>
       <c r="D69" s="70">
         <v>0.01</v>
@@ -15482,7 +15555,7 @@
       </c>
       <c r="N69" s="69">
         <f ca="1">+J4</f>
-        <v>93.627712741650726</v>
+        <v>90.720141570568231</v>
       </c>
       <c r="O69" s="70">
         <v>7.0000000000000007E-2</v>
@@ -15513,25 +15586,25 @@
       </c>
       <c r="D70" s="72">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>114.48498562482762</v>
+        <v>111.45991333062521</v>
       </c>
       <c r="E70" s="72">
-        <v>116.40339086406972</v>
+        <v>113.36581736706754</v>
       </c>
       <c r="F70" s="72">
-        <v>118.62639482307925</v>
+        <v>115.57433521920673</v>
       </c>
       <c r="G70" s="73">
-        <v>121.2453771177864</v>
+        <v>118.17625103175182</v>
       </c>
       <c r="H70" s="72">
-        <v>124.39233052675705</v>
+        <v>121.30269745817139</v>
       </c>
       <c r="I70" s="72">
-        <v>128.26524421784003</v>
+        <v>125.15037347866848</v>
       </c>
       <c r="J70" s="72">
-        <v>133.17524402622641</v>
+        <v>130.02837749070488</v>
       </c>
       <c r="M70" s="85"/>
       <c r="N70" s="71">
@@ -15539,25 +15612,25 @@
       </c>
       <c r="O70" s="72">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>110.56580193774187</v>
+        <v>107.56626883050558</v>
       </c>
       <c r="P70" s="72">
-        <v>115.01562492942708</v>
+        <v>111.9870947476915</v>
       </c>
       <c r="Q70" s="72">
-        <v>118.47659836740448</v>
+        <v>115.42551490550278</v>
       </c>
       <c r="R70" s="73">
-        <v>121.2453771177864</v>
+        <v>118.17625103175182</v>
       </c>
       <c r="S70" s="72">
-        <v>123.51074154991706</v>
+        <v>120.42685331686462</v>
       </c>
       <c r="T70" s="72">
-        <v>125.39854524335927</v>
+        <v>122.30235522112532</v>
       </c>
       <c r="U70" s="72">
-        <v>126.99591759934883</v>
+        <v>123.88931837088437</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
@@ -15566,50 +15639,50 @@
         <v>0.08</v>
       </c>
       <c r="D71" s="72">
-        <v>105.77296631523038</v>
+        <v>102.79772052766505</v>
       </c>
       <c r="E71" s="72">
-        <v>107.1095408189903</v>
+        <v>104.12549972510112</v>
       </c>
       <c r="F71" s="72">
-        <v>108.63011793129846</v>
+        <v>105.63607070497582</v>
       </c>
       <c r="G71" s="73">
-        <v>110.38488018175886</v>
+        <v>107.37928577159057</v>
       </c>
       <c r="H71" s="72">
-        <v>112.44408311181721</v>
+        <v>109.42493815096741</v>
       </c>
       <c r="I71" s="72">
-        <v>114.90920694800614</v>
+        <v>111.87384028069367</v>
       </c>
       <c r="J71" s="72">
-        <v>117.93247203012473</v>
+        <v>114.87721081715046</v>
       </c>
       <c r="M71" s="85"/>
       <c r="N71" s="71">
         <v>0.08</v>
       </c>
       <c r="O71" s="72">
-        <v>101.09762730711897</v>
+        <v>98.153147510247408</v>
       </c>
       <c r="P71" s="72">
-        <v>104.9673160048856</v>
+        <v>101.99737178580706</v>
       </c>
       <c r="Q71" s="72">
-        <v>107.97707388092628</v>
+        <v>104.98732400013124</v>
       </c>
       <c r="R71" s="73">
-        <v>110.38488018175886</v>
+        <v>107.37928577159057</v>
       </c>
       <c r="S71" s="72">
-        <v>112.35490351880367</v>
+        <v>109.33634540278457</v>
       </c>
       <c r="T71" s="72">
-        <v>113.99658963300769</v>
+        <v>110.96722842877959</v>
       </c>
       <c r="U71" s="72">
-        <v>115.38570865271878</v>
+        <v>112.34720637385227</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
@@ -15618,50 +15691,50 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="D72" s="73">
-        <v>98.234730447108362</v>
+        <v>95.302658267723658</v>
       </c>
       <c r="E72" s="73">
-        <v>99.147017973595979</v>
+        <v>96.208884363190052</v>
       </c>
       <c r="F72" s="73">
-        <v>100.16542524988142</v>
+        <v>97.220525126421776</v>
       </c>
       <c r="G72" s="73">
-        <v>101.3164822134141</v>
+        <v>98.363934224360122</v>
       </c>
       <c r="H72" s="73">
-        <v>102.63636605162513</v>
+        <v>99.675048475561496</v>
       </c>
       <c r="I72" s="73">
-        <v>104.17572482691799</v>
+        <v>101.20417942600479</v>
       </c>
       <c r="J72" s="73">
-        <v>106.00771685165329</v>
+        <v>103.02399930877064</v>
       </c>
       <c r="M72" s="85"/>
       <c r="N72" s="71">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="O72" s="73">
-        <v>93.171057869774643</v>
+        <v>90.272629800553062</v>
       </c>
       <c r="P72" s="73">
-        <v>96.56498467962443</v>
+        <v>93.644006643806009</v>
       </c>
       <c r="Q72" s="73">
-        <v>99.2047055317298</v>
+        <v>96.266188633002741</v>
       </c>
       <c r="R72" s="73">
-        <v>101.3164822134141</v>
+        <v>98.363934224360122</v>
       </c>
       <c r="S72" s="73">
-        <v>103.04429949842853</v>
+        <v>100.0802715263798</v>
       </c>
       <c r="T72" s="73">
-        <v>104.48414723594057</v>
+        <v>101.51055261139621</v>
       </c>
       <c r="U72" s="73">
-        <v>105.7024799369123</v>
+        <v>102.72079045256393</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
@@ -15670,50 +15743,50 @@
         <v>0.09</v>
       </c>
       <c r="D73" s="72">
-        <v>91.649855786546738</v>
+        <v>88.755551371826101</v>
       </c>
       <c r="E73" s="72">
-        <v>92.249628282111033</v>
+        <v>89.351300808214859</v>
       </c>
       <c r="F73" s="72">
-        <v>92.904662994088312</v>
+        <v>90.001941781853276</v>
       </c>
       <c r="G73" s="73">
-        <v>93.627712741650726</v>
+        <v>90.720141570568231</v>
       </c>
       <c r="H73" s="72">
-        <v>94.435781283694595</v>
+        <v>91.522789878128847</v>
       </c>
       <c r="I73" s="72">
-        <v>95.352055564169405</v>
+        <v>92.432918118765784</v>
       </c>
       <c r="J73" s="72">
-        <v>96.408997304604426</v>
+        <v>93.482770272401893</v>
       </c>
       <c r="M73" s="85"/>
       <c r="N73" s="71">
         <v>0.09</v>
       </c>
       <c r="O73" s="72">
-        <v>86.432314768335374</v>
+        <v>83.573007750832005</v>
       </c>
       <c r="P73" s="72">
-        <v>89.430397257216768</v>
+        <v>86.550980175722088</v>
       </c>
       <c r="Q73" s="72">
-        <v>91.762239193013414</v>
+        <v>88.867180950636609</v>
       </c>
       <c r="R73" s="73">
-        <v>93.627712741650726</v>
+        <v>90.720141570568231</v>
       </c>
       <c r="S73" s="72">
-        <v>95.154009281444885</v>
+        <v>92.236200259603194</v>
       </c>
       <c r="T73" s="72">
-        <v>96.425923064606678</v>
+        <v>93.49958250046565</v>
       </c>
       <c r="U73" s="72">
-        <v>97.502157804205126</v>
+        <v>94.568598242733884</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
@@ -15722,50 +15795,50 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="D74" s="72">
-        <v>85.849794883844709</v>
+        <v>82.988806052119301</v>
       </c>
       <c r="E74" s="72">
-        <v>86.217715641718826</v>
+        <v>83.354235700060997</v>
       </c>
       <c r="F74" s="72">
-        <v>86.607516819409554</v>
+        <v>83.741397620344671</v>
       </c>
       <c r="G74" s="73">
-        <v>87.023887078306032</v>
+        <v>84.154948728472121</v>
       </c>
       <c r="H74" s="72">
-        <v>87.472957744840443</v>
+        <v>84.600978837022708</v>
       </c>
       <c r="I74" s="72">
-        <v>87.962903920922258</v>
+        <v>85.087607696102211</v>
       </c>
       <c r="J74" s="72">
-        <v>88.504873472791687</v>
+        <v>85.625907692218533</v>
       </c>
       <c r="M74" s="85"/>
       <c r="N74" s="71">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="O74" s="72">
-        <v>80.628589645205423</v>
+        <v>77.802952437303645</v>
       </c>
       <c r="P74" s="72">
-        <v>83.293296908997334</v>
+        <v>80.449617558623842</v>
       </c>
       <c r="Q74" s="72">
-        <v>85.365847003057723</v>
+        <v>82.50813487520621</v>
       </c>
       <c r="R74" s="73">
-        <v>87.023887078306032</v>
+        <v>84.154948728472121</v>
       </c>
       <c r="S74" s="72">
-        <v>88.380465321691005</v>
+        <v>85.502341881144218</v>
       </c>
       <c r="T74" s="72">
-        <v>89.510947191178488</v>
+        <v>86.625169508370959</v>
       </c>
       <c r="U74" s="72">
-        <v>90.467508773052501</v>
+        <v>87.575254423716672</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
@@ -15774,50 +15847,50 @@
         <v>0.1</v>
       </c>
       <c r="D75" s="72">
-        <v>80.703465049646198</v>
+        <v>77.872081384146128</v>
       </c>
       <c r="E75" s="72">
-        <v>80.898592746221439</v>
+        <v>78.065875651556993</v>
       </c>
       <c r="F75" s="72">
-        <v>81.09372044279668</v>
+        <v>78.259669918967873</v>
       </c>
       <c r="G75" s="73">
-        <v>81.288848139371936</v>
+        <v>78.453464186378724</v>
       </c>
       <c r="H75" s="72">
-        <v>81.483975835947177</v>
+        <v>78.64725845378959</v>
       </c>
       <c r="I75" s="72">
-        <v>81.679103532522419</v>
+        <v>78.841052721200455</v>
       </c>
       <c r="J75" s="72">
-        <v>81.874231229097674</v>
+        <v>79.034846988611349</v>
       </c>
       <c r="M75" s="85"/>
       <c r="N75" s="71">
         <v>0.1</v>
       </c>
       <c r="O75" s="72">
-        <v>75.574394168239763</v>
+        <v>72.778060640774683</v>
       </c>
       <c r="P75" s="72">
-        <v>77.955416656211511</v>
+        <v>75.142812118109703</v>
       </c>
       <c r="Q75" s="72">
-        <v>79.807323035745085</v>
+        <v>76.98206326714805</v>
       </c>
       <c r="R75" s="73">
-        <v>81.288848139371936</v>
+        <v>78.453464186378724</v>
       </c>
       <c r="S75" s="72">
-        <v>82.501005042339358</v>
+        <v>79.657337665749282</v>
       </c>
       <c r="T75" s="72">
-        <v>83.511135794812219</v>
+        <v>80.660565565224744</v>
       </c>
       <c r="U75" s="72">
-        <v>84.365861816135393</v>
+        <v>81.509450710934743</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
@@ -15826,50 +15899,50 @@
         <v>0.105</v>
       </c>
       <c r="D76" s="72">
-        <v>76.107388876657666</v>
+        <v>73.302485589193836</v>
       </c>
       <c r="E76" s="72">
-        <v>76.17349492773215</v>
+        <v>73.36813576109985</v>
       </c>
       <c r="F76" s="72">
-        <v>76.225396372790613</v>
+        <v>73.41967928449715</v>
       </c>
       <c r="G76" s="73">
-        <v>76.260429848205078</v>
+        <v>73.454471162790327</v>
       </c>
       <c r="H76" s="72">
-        <v>76.275221760046733</v>
+        <v>73.469161066958534</v>
       </c>
       <c r="I76" s="72">
-        <v>76.265434630407128</v>
+        <v>73.459441431117895</v>
       </c>
       <c r="J76" s="72">
-        <v>76.225396372790613</v>
+        <v>73.41967928449715</v>
       </c>
       <c r="M76" s="86"/>
       <c r="N76" s="71">
         <v>0.105</v>
       </c>
       <c r="O76" s="72">
-        <v>71.130528091087228</v>
+        <v>68.359946127004619</v>
       </c>
       <c r="P76" s="72">
-        <v>73.267987156552977</v>
+        <v>70.482664891915306</v>
       </c>
       <c r="Q76" s="72">
-        <v>74.930455318581934</v>
+        <v>72.133668375734757</v>
       </c>
       <c r="R76" s="73">
-        <v>76.260429848205078</v>
+        <v>73.454471162790327</v>
       </c>
       <c r="S76" s="72">
-        <v>77.348590826987646</v>
+        <v>74.535127988563033</v>
       </c>
       <c r="T76" s="72">
-        <v>78.255391642639793</v>
+        <v>75.435675343373646</v>
       </c>
       <c r="U76" s="72">
-        <v>79.022684640499321</v>
+        <v>76.197676951290305</v>
       </c>
     </row>
   </sheetData>
